--- a/Daily_Report/Top 7 broker List with its Turnover 2024-10-29.xlsx
+++ b/Daily_Report/Top 7 broker List with its Turnover 2024-10-29.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="278">
   <si>
     <t>Date: 2024-10-29</t>
   </si>
@@ -59,109 +59,109 @@
     <t>7</t>
   </si>
   <si>
+    <t>Linch Stock Market Limited</t>
+  </si>
+  <si>
+    <t>Online Securities Pvt.Ltd</t>
+  </si>
+  <si>
+    <t>Sani Securities Company Limited</t>
+  </si>
+  <si>
     <t>Naasa Securities Co. Ltd.</t>
   </si>
   <si>
-    <t>Sani Securities Company Limited</t>
-  </si>
-  <si>
-    <t>Imperial Securities Co .Pvt.Limited</t>
-  </si>
-  <si>
-    <t>Linch Stock Market Limited</t>
-  </si>
-  <si>
-    <t>Vision Securities Pvt.Limited</t>
-  </si>
-  <si>
-    <t>Dynamic Money Managers Securities Pvt.Ltd</t>
-  </si>
-  <si>
-    <t>Online Securities Pvt.Ltd</t>
+    <t>Kohinoor Investment and Securities Pvt.Ltd</t>
+  </si>
+  <si>
+    <t>Araya Tara Investment And Securities Pvt. Ltd.</t>
+  </si>
+  <si>
+    <t>ABC Securities Pvt. Limited</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>42</t>
   </si>
   <si>
     <t>58</t>
   </si>
   <si>
-    <t>42</t>
-  </si>
-  <si>
-    <t>45</t>
-  </si>
-  <si>
-    <t>41</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>44</t>
-  </si>
-  <si>
-    <t>49</t>
-  </si>
-  <si>
-    <t>571,828,357.2</t>
-  </si>
-  <si>
-    <t>479,444,515.57</t>
-  </si>
-  <si>
-    <t>466,795,407.29</t>
-  </si>
-  <si>
-    <t>448,186,949.47</t>
-  </si>
-  <si>
-    <t>447,873,072.05</t>
-  </si>
-  <si>
-    <t>377,924,809.7</t>
-  </si>
-  <si>
-    <t>365,060,136.05</t>
-  </si>
-  <si>
-    <t>295,293,276.89</t>
-  </si>
-  <si>
-    <t>232,746,356.44</t>
-  </si>
-  <si>
-    <t>256,406,729.2</t>
-  </si>
-  <si>
-    <t>338,566,942.27</t>
-  </si>
-  <si>
-    <t>253,291,212.8</t>
-  </si>
-  <si>
-    <t>153,497,177.69</t>
-  </si>
-  <si>
-    <t>155,657,736.5</t>
-  </si>
-  <si>
-    <t>276,535,080.3</t>
-  </si>
-  <si>
-    <t>246,698,159.13</t>
-  </si>
-  <si>
-    <t>210,388,678.1</t>
-  </si>
-  <si>
-    <t>109,620,007.2</t>
-  </si>
-  <si>
-    <t>194,581,859.25</t>
-  </si>
-  <si>
-    <t>224,427,632.0</t>
-  </si>
-  <si>
-    <t>209,402,399.55</t>
+    <t>35</t>
+  </si>
+  <si>
+    <t>57</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>903,620,354.68</t>
+  </si>
+  <si>
+    <t>701,149,190.4</t>
+  </si>
+  <si>
+    <t>586,814,051.33</t>
+  </si>
+  <si>
+    <t>516,204,230.6</t>
+  </si>
+  <si>
+    <t>496,245,923.7</t>
+  </si>
+  <si>
+    <t>460,155,922.93</t>
+  </si>
+  <si>
+    <t>358,653,056.9</t>
+  </si>
+  <si>
+    <t>798,651,138.08</t>
+  </si>
+  <si>
+    <t>239,925,507.7</t>
+  </si>
+  <si>
+    <t>212,052,318.1</t>
+  </si>
+  <si>
+    <t>280,633,798.39</t>
+  </si>
+  <si>
+    <t>89,224,056.2</t>
+  </si>
+  <si>
+    <t>88,651,511.04</t>
+  </si>
+  <si>
+    <t>209,883,985.9</t>
+  </si>
+  <si>
+    <t>104,969,216.6</t>
+  </si>
+  <si>
+    <t>461,223,682.7</t>
+  </si>
+  <si>
+    <t>374,761,733.23</t>
+  </si>
+  <si>
+    <t>235,570,432.2</t>
+  </si>
+  <si>
+    <t>407,021,867.5</t>
+  </si>
+  <si>
+    <t>371,504,411.9</t>
+  </si>
+  <si>
+    <t>148,769,071.0</t>
   </si>
   <si>
     <t>Top 5 Buy</t>
@@ -179,352 +179,346 @@
     <t>% of turnover</t>
   </si>
   <si>
+    <t>JFL</t>
+  </si>
+  <si>
+    <t>587,777,980.5</t>
+  </si>
+  <si>
+    <t>SFCL</t>
+  </si>
+  <si>
+    <t>107,107,706.5</t>
+  </si>
+  <si>
+    <t>RNLI</t>
+  </si>
+  <si>
+    <t>23,541,611.0</t>
+  </si>
+  <si>
+    <t>LICN</t>
+  </si>
+  <si>
+    <t>21,116,220.0</t>
+  </si>
+  <si>
+    <t>NFS</t>
+  </si>
+  <si>
+    <t>18,934,512.0</t>
+  </si>
+  <si>
+    <t>JBBL</t>
+  </si>
+  <si>
+    <t>82,938,484.0</t>
+  </si>
+  <si>
+    <t>44,994,328.0</t>
+  </si>
+  <si>
+    <t>ICFC</t>
+  </si>
+  <si>
+    <t>32,912,170.0</t>
+  </si>
+  <si>
+    <t>EDBL</t>
+  </si>
+  <si>
+    <t>23,132,501.0</t>
+  </si>
+  <si>
+    <t>GMFIL</t>
+  </si>
+  <si>
+    <t>7,387,200.0</t>
+  </si>
+  <si>
+    <t>86,316,420.0</t>
+  </si>
+  <si>
+    <t>SPDL</t>
+  </si>
+  <si>
+    <t>25,456,200.0</t>
+  </si>
+  <si>
+    <t>PRSF</t>
+  </si>
+  <si>
+    <t>16,541,742.0</t>
+  </si>
+  <si>
+    <t>UPCL</t>
+  </si>
+  <si>
+    <t>15,825,585.0</t>
+  </si>
+  <si>
+    <t>MDB</t>
+  </si>
+  <si>
+    <t>10,944,000.0</t>
+  </si>
+  <si>
+    <t>IGI</t>
+  </si>
+  <si>
+    <t>44,241,595.2</t>
+  </si>
+  <si>
+    <t>AKJCL</t>
+  </si>
+  <si>
+    <t>37,284,041.5</t>
+  </si>
+  <si>
+    <t>SAPDBL</t>
+  </si>
+  <si>
+    <t>21,495,820.0</t>
+  </si>
+  <si>
+    <t>20,732,920.0</t>
+  </si>
+  <si>
+    <t>ULHC</t>
+  </si>
+  <si>
+    <t>19,179,396.2</t>
+  </si>
+  <si>
+    <t>BFC</t>
+  </si>
+  <si>
+    <t>37,457,500.0</t>
+  </si>
+  <si>
+    <t>17,677,076.0</t>
+  </si>
+  <si>
+    <t>11,325,650.0</t>
+  </si>
+  <si>
+    <t>5,409,439.0</t>
+  </si>
+  <si>
+    <t>SNLI</t>
+  </si>
+  <si>
+    <t>3,400,717.2</t>
+  </si>
+  <si>
+    <t>16,992,042.0</t>
+  </si>
+  <si>
+    <t>NIFRA</t>
+  </si>
+  <si>
+    <t>15,982,075.0</t>
+  </si>
+  <si>
+    <t>11,152,934.0</t>
+  </si>
+  <si>
+    <t>CHDC</t>
+  </si>
+  <si>
+    <t>6,381,622.9</t>
+  </si>
+  <si>
     <t>SAHAS</t>
   </si>
   <si>
-    <t>14,465,548.7</t>
-  </si>
-  <si>
-    <t>MEN</t>
-  </si>
-  <si>
-    <t>13,067,393.7</t>
-  </si>
-  <si>
-    <t>MLBBL</t>
-  </si>
-  <si>
-    <t>10,172,669.4</t>
+    <t>6,104,521.5</t>
+  </si>
+  <si>
+    <t>PRVU</t>
+  </si>
+  <si>
+    <t>173,825,568.9</t>
+  </si>
+  <si>
+    <t>4,170,495.0</t>
+  </si>
+  <si>
+    <t>UNHPL</t>
+  </si>
+  <si>
+    <t>3,249,736.1</t>
+  </si>
+  <si>
+    <t>2,839,680.0</t>
+  </si>
+  <si>
+    <t>CFCL</t>
+  </si>
+  <si>
+    <t>2,288,580.5</t>
+  </si>
+  <si>
+    <t>Sell Amount</t>
+  </si>
+  <si>
+    <t>28,990,753.0</t>
+  </si>
+  <si>
+    <t>15,959,200.0</t>
+  </si>
+  <si>
+    <t>15,065,724.0</t>
+  </si>
+  <si>
+    <t>PFL</t>
+  </si>
+  <si>
+    <t>8,893,881.0</t>
+  </si>
+  <si>
+    <t>7,118,942.0</t>
+  </si>
+  <si>
+    <t>297,112,550.0</t>
+  </si>
+  <si>
+    <t>37,347,654.0</t>
+  </si>
+  <si>
+    <t>MFIL</t>
+  </si>
+  <si>
+    <t>35,943,960.0</t>
+  </si>
+  <si>
+    <t>KRBL</t>
+  </si>
+  <si>
+    <t>23,892,009.3</t>
+  </si>
+  <si>
+    <t>GBIME</t>
+  </si>
+  <si>
+    <t>8,945,105.0</t>
+  </si>
+  <si>
+    <t>211,061,367.0</t>
+  </si>
+  <si>
+    <t>FMDBL</t>
+  </si>
+  <si>
+    <t>40,543,746.0</t>
+  </si>
+  <si>
+    <t>32,095,895.5</t>
+  </si>
+  <si>
+    <t>SPC</t>
+  </si>
+  <si>
+    <t>13,942,293.4</t>
+  </si>
+  <si>
+    <t>12,115,662.5</t>
+  </si>
+  <si>
+    <t>NGPL</t>
+  </si>
+  <si>
+    <t>67,198,355.7</t>
+  </si>
+  <si>
+    <t>NRN</t>
+  </si>
+  <si>
+    <t>41,809,329.0</t>
+  </si>
+  <si>
+    <t>21,656,094.8</t>
+  </si>
+  <si>
+    <t>SWBBL</t>
+  </si>
+  <si>
+    <t>16,733,148.0</t>
   </si>
   <si>
     <t>HRL</t>
   </si>
   <si>
-    <t>9,611,858.0</t>
-  </si>
-  <si>
-    <t>NGPL</t>
-  </si>
-  <si>
-    <t>8,941,128.8</t>
-  </si>
-  <si>
-    <t>MPFL</t>
-  </si>
-  <si>
-    <t>21,520,196.8</t>
-  </si>
-  <si>
-    <t>GBBL</t>
-  </si>
-  <si>
-    <t>12,402,680.0</t>
-  </si>
-  <si>
-    <t>SNLI</t>
-  </si>
-  <si>
-    <t>9,028,320.19</t>
-  </si>
-  <si>
-    <t>NICA</t>
-  </si>
-  <si>
-    <t>9,006,571.8</t>
-  </si>
-  <si>
-    <t>MAKAR</t>
-  </si>
-  <si>
-    <t>8,921,900.0</t>
+    <t>10,553,032.0</t>
+  </si>
+  <si>
+    <t>210,878,910.0</t>
+  </si>
+  <si>
+    <t>HIDCL</t>
+  </si>
+  <si>
+    <t>159,356,399.5</t>
   </si>
   <si>
     <t>SHPC</t>
   </si>
   <si>
-    <t>29,464,534.9</t>
-  </si>
-  <si>
-    <t>SHL</t>
-  </si>
-  <si>
-    <t>12,557,844.4</t>
-  </si>
-  <si>
-    <t>KBL</t>
-  </si>
-  <si>
-    <t>11,858,407.0</t>
-  </si>
-  <si>
-    <t>HURJA</t>
-  </si>
-  <si>
-    <t>11,527,026.2</t>
-  </si>
-  <si>
-    <t>10,189,497.8</t>
-  </si>
-  <si>
-    <t>SFCL</t>
-  </si>
-  <si>
-    <t>160,406,193.0</t>
-  </si>
-  <si>
-    <t>JFL</t>
-  </si>
-  <si>
-    <t>37,759,310.5</t>
-  </si>
-  <si>
-    <t>NFS</t>
-  </si>
-  <si>
-    <t>28,831,594.0</t>
-  </si>
-  <si>
-    <t>SICL</t>
-  </si>
-  <si>
-    <t>10,931,215.0</t>
-  </si>
-  <si>
-    <t>DOLTI</t>
-  </si>
-  <si>
-    <t>9,788,260.0</t>
-  </si>
-  <si>
-    <t>STC</t>
-  </si>
-  <si>
-    <t>35,205,545.0</t>
-  </si>
-  <si>
-    <t>LSL</t>
-  </si>
-  <si>
-    <t>20,576,661.2</t>
-  </si>
-  <si>
-    <t>GHL</t>
-  </si>
-  <si>
-    <t>17,431,299.0</t>
-  </si>
-  <si>
-    <t>UPPER</t>
-  </si>
-  <si>
-    <t>17,421,444.89</t>
-  </si>
-  <si>
-    <t>RLFL</t>
-  </si>
-  <si>
-    <t>6,585,215.7</t>
-  </si>
-  <si>
-    <t>17,077,078.1</t>
-  </si>
-  <si>
-    <t>SJLIC</t>
-  </si>
-  <si>
-    <t>13,928,536.1</t>
-  </si>
-  <si>
-    <t>NLG</t>
-  </si>
-  <si>
-    <t>6,857,600.0</t>
-  </si>
-  <si>
-    <t>KSBBLP</t>
-  </si>
-  <si>
-    <t>6,715,926.0</t>
-  </si>
-  <si>
-    <t>NICL</t>
-  </si>
-  <si>
-    <t>6,482,180.0</t>
-  </si>
-  <si>
-    <t>NIFRA</t>
-  </si>
-  <si>
-    <t>7,530,455.5</t>
+    <t>12,656,600.0</t>
+  </si>
+  <si>
+    <t>MBJC</t>
+  </si>
+  <si>
+    <t>3,101,728.0</t>
+  </si>
+  <si>
+    <t>SGIC</t>
+  </si>
+  <si>
+    <t>2,181,712.5</t>
+  </si>
+  <si>
+    <t>228,277,784.0</t>
+  </si>
+  <si>
+    <t>SBI</t>
+  </si>
+  <si>
+    <t>38,393,066.0</t>
+  </si>
+  <si>
+    <t>HDHPC</t>
+  </si>
+  <si>
+    <t>12,428,508.0</t>
+  </si>
+  <si>
+    <t>11,691,532.0</t>
+  </si>
+  <si>
+    <t>8,769,836.0</t>
+  </si>
+  <si>
+    <t>49,168,200.0</t>
+  </si>
+  <si>
+    <t>37,535,649.8</t>
+  </si>
+  <si>
+    <t>MMKJL</t>
+  </si>
+  <si>
+    <t>29,824,701.0</t>
+  </si>
+  <si>
+    <t>3,727,690.0</t>
   </si>
   <si>
     <t>PROFL</t>
   </si>
   <si>
-    <t>5,360,297.09</t>
-  </si>
-  <si>
-    <t>5,320,970.5</t>
-  </si>
-  <si>
-    <t>RIDI</t>
-  </si>
-  <si>
-    <t>4,755,149.3</t>
-  </si>
-  <si>
-    <t>4,663,529.0</t>
-  </si>
-  <si>
-    <t>Sell Amount</t>
-  </si>
-  <si>
-    <t>31,097,521.2</t>
-  </si>
-  <si>
-    <t>MMKJL</t>
-  </si>
-  <si>
-    <t>25,940,380.0</t>
-  </si>
-  <si>
-    <t>MFIL</t>
-  </si>
-  <si>
-    <t>13,928,906.2</t>
-  </si>
-  <si>
-    <t>LICN</t>
-  </si>
-  <si>
-    <t>12,558,122.3</t>
-  </si>
-  <si>
-    <t>11,104,751.0</t>
-  </si>
-  <si>
-    <t>75,802,620.0</t>
-  </si>
-  <si>
-    <t>22,166,287.1</t>
-  </si>
-  <si>
-    <t>6,284,200.5</t>
-  </si>
-  <si>
-    <t>6,248,335.1</t>
-  </si>
-  <si>
-    <t>NRN</t>
-  </si>
-  <si>
-    <t>4,253,271.09</t>
-  </si>
-  <si>
-    <t>ICFC</t>
-  </si>
-  <si>
-    <t>11,664,329.9</t>
-  </si>
-  <si>
-    <t>SGIC</t>
-  </si>
-  <si>
-    <t>11,569,066.0</t>
-  </si>
-  <si>
-    <t>10,413,457.0</t>
-  </si>
-  <si>
-    <t>7,528,382.2</t>
-  </si>
-  <si>
-    <t>6,434,508.9</t>
-  </si>
-  <si>
-    <t>CFCL</t>
-  </si>
-  <si>
-    <t>15,061,683.1</t>
-  </si>
-  <si>
-    <t>PFL</t>
-  </si>
-  <si>
-    <t>12,257,392.8</t>
-  </si>
-  <si>
-    <t>9,235,170.0</t>
-  </si>
-  <si>
-    <t>5,035,589.0</t>
-  </si>
-  <si>
-    <t>GFCL</t>
-  </si>
-  <si>
-    <t>4,167,462.0</t>
-  </si>
-  <si>
-    <t>MBJC</t>
-  </si>
-  <si>
-    <t>11,452,102.2</t>
-  </si>
-  <si>
-    <t>7,739,700.0</t>
-  </si>
-  <si>
-    <t>7,526,825.5</t>
-  </si>
-  <si>
-    <t>SANIMA</t>
-  </si>
-  <si>
-    <t>5,610,970.2</t>
-  </si>
-  <si>
-    <t>5,470,734.0</t>
-  </si>
-  <si>
-    <t>51,837,796.8</t>
-  </si>
-  <si>
-    <t>SPDL</t>
-  </si>
-  <si>
-    <t>26,189,939.4</t>
-  </si>
-  <si>
-    <t>18,444,828.0</t>
-  </si>
-  <si>
-    <t>11,209,735.1</t>
-  </si>
-  <si>
-    <t>SRLI</t>
-  </si>
-  <si>
-    <t>6,530,395.4</t>
-  </si>
-  <si>
-    <t>27,145,284.8</t>
-  </si>
-  <si>
-    <t>HIDCLP</t>
-  </si>
-  <si>
-    <t>14,364,653.2</t>
-  </si>
-  <si>
-    <t>11,701,313.5</t>
-  </si>
-  <si>
-    <t>10,950,126.5</t>
-  </si>
-  <si>
-    <t>6,194,572.5</t>
+    <t>3,503,352.0</t>
   </si>
   <si>
     <t>Top Traded Stocks</t>
@@ -542,115 +536,112 @@
     <t>Percentage (%)</t>
   </si>
   <si>
-    <t>303,316,865.5</t>
-  </si>
-  <si>
-    <t>173,488,565.0</t>
-  </si>
-  <si>
-    <t>SAPDBL</t>
-  </si>
-  <si>
-    <t>131,953,173.7</t>
-  </si>
-  <si>
-    <t>126,380,045.6</t>
-  </si>
-  <si>
-    <t>PHCL</t>
-  </si>
-  <si>
-    <t>120,685,601.6</t>
+    <t>625,590,491.2</t>
+  </si>
+  <si>
+    <t>424,647,020.0</t>
+  </si>
+  <si>
+    <t>GRDBL</t>
+  </si>
+  <si>
+    <t>237,892,159.0</t>
+  </si>
+  <si>
+    <t>208,775,494.8</t>
+  </si>
+  <si>
+    <t>188,840,465.9</t>
+  </si>
+  <si>
+    <t>Finance</t>
+  </si>
+  <si>
+    <t>1,409,886,027.7</t>
   </si>
   <si>
     <t>Hydro Power</t>
   </si>
   <si>
-    <t>1,546,225,396.6</t>
+    <t>890,912,604.6</t>
+  </si>
+  <si>
+    <t>Development Banks</t>
+  </si>
+  <si>
+    <t>805,253,070.2</t>
   </si>
   <si>
     <t>Promoter Shares/debenture</t>
   </si>
   <si>
-    <t>1,448,996,830.25</t>
-  </si>
-  <si>
-    <t>Finance</t>
-  </si>
-  <si>
-    <t>1,305,864,903.3</t>
+    <t>768,887,572.8</t>
+  </si>
+  <si>
+    <t>Investment</t>
+  </si>
+  <si>
+    <t>545,342,197.9</t>
   </si>
   <si>
     <t>Commercial Banks</t>
   </si>
   <si>
-    <t>386,217,848.0</t>
-  </si>
-  <si>
-    <t>Development Banks</t>
-  </si>
-  <si>
-    <t>379,657,255.6</t>
+    <t>512,577,748.5</t>
+  </si>
+  <si>
+    <t>Life Insurance</t>
+  </si>
+  <si>
+    <t>441,949,909.4</t>
   </si>
   <si>
     <t>Non Life Insurance</t>
   </si>
   <si>
-    <t>242,026,997.3</t>
+    <t>182,315,581.2</t>
   </si>
   <si>
     <t>Microfinance</t>
   </si>
   <si>
-    <t>225,833,974.1</t>
-  </si>
-  <si>
-    <t>Investment</t>
-  </si>
-  <si>
-    <t>180,981,325.3</t>
+    <t>118,312,534.9</t>
+  </si>
+  <si>
+    <t>Manufacturing And Processing</t>
+  </si>
+  <si>
+    <t>86,652,771.1</t>
   </si>
   <si>
     <t>Hotels And Tourism</t>
   </si>
   <si>
-    <t>91,934,874.0</t>
-  </si>
-  <si>
-    <t>Manufacturing And Processing</t>
-  </si>
-  <si>
-    <t>87,312,462.7</t>
-  </si>
-  <si>
-    <t>Life Insurance</t>
-  </si>
-  <si>
-    <t>84,921,164.59</t>
+    <t>28,249,307.5</t>
+  </si>
+  <si>
+    <t>Others</t>
+  </si>
+  <si>
+    <t>20,218,432.3</t>
+  </si>
+  <si>
+    <t>Mutual Fund</t>
+  </si>
+  <si>
+    <t>12,421,805.08</t>
   </si>
   <si>
     <t>Trading</t>
   </si>
   <si>
-    <t>39,803,588.9</t>
-  </si>
-  <si>
-    <t>Others</t>
-  </si>
-  <si>
-    <t>30,702,570.0</t>
-  </si>
-  <si>
-    <t>Mutual Fund</t>
-  </si>
-  <si>
-    <t>11,039,499.36</t>
+    <t>2,840,460.0</t>
   </si>
   <si>
     <t>Tradings</t>
   </si>
   <si>
-    <t>909,362.0</t>
+    <t>126,430.0</t>
   </si>
   <si>
     <t>Total</t>
@@ -662,211 +653,202 @@
     <t>100%</t>
   </si>
   <si>
-    <t>96,331,818.4</t>
-  </si>
-  <si>
-    <t>79,202,418.7</t>
-  </si>
-  <si>
-    <t>46,771,722.8</t>
-  </si>
-  <si>
-    <t>17,654,200.89</t>
-  </si>
-  <si>
-    <t>13,227,877.2</t>
-  </si>
-  <si>
-    <t>64,841,024.5</t>
-  </si>
-  <si>
-    <t>57,124,901.0</t>
-  </si>
-  <si>
-    <t>39,546,170.0</t>
-  </si>
-  <si>
-    <t>19,740,465.0</t>
-  </si>
-  <si>
-    <t>18,742,008.0</t>
-  </si>
-  <si>
-    <t>92,168,748.8</t>
-  </si>
-  <si>
-    <t>62,061,816.9</t>
-  </si>
-  <si>
-    <t>29,447,554.0</t>
-  </si>
-  <si>
-    <t>22,339,628.9</t>
-  </si>
-  <si>
-    <t>14,601,021.4</t>
-  </si>
-  <si>
-    <t>237,694,701.9</t>
-  </si>
-  <si>
-    <t>38,323,727.29</t>
-  </si>
-  <si>
-    <t>28,052,221.1</t>
-  </si>
-  <si>
-    <t>11,818,939.5</t>
-  </si>
-  <si>
-    <t>8,256,416.5</t>
-  </si>
-  <si>
-    <t>67,686,718.2</t>
-  </si>
-  <si>
-    <t>60,867,508.4</t>
-  </si>
-  <si>
-    <t>29,867,530.6</t>
-  </si>
-  <si>
-    <t>15,204,715.6</t>
-  </si>
-  <si>
-    <t>43,735,894.3</t>
-  </si>
-  <si>
-    <t>41,666,000.4</t>
-  </si>
-  <si>
-    <t>15,618,605.0</t>
-  </si>
-  <si>
-    <t>15,022,957.1</t>
-  </si>
-  <si>
-    <t>14,864,031.1</t>
-  </si>
-  <si>
-    <t>35,420,720.5</t>
-  </si>
-  <si>
-    <t>34,503,530.29</t>
-  </si>
-  <si>
-    <t>33,720,622.1</t>
-  </si>
-  <si>
-    <t>13,640,897.4</t>
-  </si>
-  <si>
-    <t>9,729,185.5</t>
-  </si>
-  <si>
-    <t>90,546,090.9</t>
-  </si>
-  <si>
-    <t>67,625,292.3</t>
-  </si>
-  <si>
-    <t>50,444,157.1</t>
-  </si>
-  <si>
-    <t>19,952,513.39</t>
-  </si>
-  <si>
-    <t>13,806,895.9</t>
-  </si>
-  <si>
-    <t>101,199,766.6</t>
-  </si>
-  <si>
-    <t>66,195,585.4</t>
-  </si>
-  <si>
-    <t>41,357,341.7</t>
-  </si>
-  <si>
-    <t>8,258,992.9</t>
-  </si>
-  <si>
-    <t>7,136,494.5</t>
-  </si>
-  <si>
-    <t>53,628,382.9</t>
-  </si>
-  <si>
-    <t>52,754,271.5</t>
-  </si>
-  <si>
-    <t>47,602,337.0</t>
-  </si>
-  <si>
-    <t>13,309,633.5</t>
-  </si>
-  <si>
-    <t>11,933,523.9</t>
-  </si>
-  <si>
-    <t>44,296,240.3</t>
-  </si>
-  <si>
-    <t>25,356,383.6</t>
-  </si>
-  <si>
-    <t>14,563,179.6</t>
-  </si>
-  <si>
-    <t>7,724,428.0</t>
-  </si>
-  <si>
-    <t>4,914,684.2</t>
-  </si>
-  <si>
-    <t>53,806,885.7</t>
-  </si>
-  <si>
-    <t>36,071,602.29</t>
-  </si>
-  <si>
-    <t>34,842,505.4</t>
-  </si>
-  <si>
-    <t>23,579,096.9</t>
-  </si>
-  <si>
-    <t>13,731,715.7</t>
-  </si>
-  <si>
-    <t>63,177,520.8</t>
-  </si>
-  <si>
-    <t>59,564,669.0</t>
-  </si>
-  <si>
-    <t>43,402,536.6</t>
-  </si>
-  <si>
-    <t>23,724,052.4</t>
-  </si>
-  <si>
-    <t>10,861,944.4</t>
-  </si>
-  <si>
-    <t>51,720,979.1</t>
-  </si>
-  <si>
-    <t>41,652,368.9</t>
-  </si>
-  <si>
-    <t>32,124,182.3</t>
-  </si>
-  <si>
-    <t>25,314,199.8</t>
-  </si>
-  <si>
-    <t>21,578,513.4</t>
+    <t>725,418,358.2</t>
+  </si>
+  <si>
+    <t>28,466,564.6</t>
+  </si>
+  <si>
+    <t>11,080,929.5</t>
+  </si>
+  <si>
+    <t>6,319,423.4</t>
+  </si>
+  <si>
+    <t>114,034,144.0</t>
+  </si>
+  <si>
+    <t>45,667,516.8</t>
+  </si>
+  <si>
+    <t>45,075,095.0</t>
+  </si>
+  <si>
+    <t>11,147,916.7</t>
+  </si>
+  <si>
+    <t>9,512,660.6</t>
+  </si>
+  <si>
+    <t>94,149,999.0</t>
+  </si>
+  <si>
+    <t>47,825,194.3</t>
+  </si>
+  <si>
+    <t>33,789,403.6</t>
+  </si>
+  <si>
+    <t>14,322,552.0</t>
+  </si>
+  <si>
+    <t>7,022,333.9</t>
+  </si>
+  <si>
+    <t>80,651,354.9</t>
+  </si>
+  <si>
+    <t>49,433,188.7</t>
+  </si>
+  <si>
+    <t>44,963,916.2</t>
+  </si>
+  <si>
+    <t>43,025,517.3</t>
+  </si>
+  <si>
+    <t>25,012,362.0</t>
+  </si>
+  <si>
+    <t>58,193,342.5</t>
+  </si>
+  <si>
+    <t>7,178,042.9</t>
+  </si>
+  <si>
+    <t>6,993,270.0</t>
+  </si>
+  <si>
+    <t>3,564,623.9</t>
+  </si>
+  <si>
+    <t>25,346,771.3</t>
+  </si>
+  <si>
+    <t>22,793,075.9</t>
+  </si>
+  <si>
+    <t>15,584,022.0</t>
+  </si>
+  <si>
+    <t>11,194,734.0</t>
+  </si>
+  <si>
+    <t>9,864,303.69</t>
+  </si>
+  <si>
+    <t>174,224,931.9</t>
+  </si>
+  <si>
+    <t>8,139,321.9</t>
+  </si>
+  <si>
+    <t>7,882,388.5</t>
+  </si>
+  <si>
+    <t>7,077,257.4</t>
+  </si>
+  <si>
+    <t>6,464,682.0</t>
+  </si>
+  <si>
+    <t>52,642,591.0</t>
+  </si>
+  <si>
+    <t>18,414,431.39</t>
+  </si>
+  <si>
+    <t>15,353,259.2</t>
+  </si>
+  <si>
+    <t>7,301,383.2</t>
+  </si>
+  <si>
+    <t>3,404,753.0</t>
+  </si>
+  <si>
+    <t>382,153,693.8</t>
+  </si>
+  <si>
+    <t>29,411,382.3</t>
+  </si>
+  <si>
+    <t>18,680,664.1</t>
+  </si>
+  <si>
+    <t>8,341,100.0</t>
+  </si>
+  <si>
+    <t>7,305,999.5</t>
+  </si>
+  <si>
+    <t>211,085,507.0</t>
+  </si>
+  <si>
+    <t>51,352,732.4</t>
+  </si>
+  <si>
+    <t>49,499,280.7</t>
+  </si>
+  <si>
+    <t>17,835,953.5</t>
+  </si>
+  <si>
+    <t>12,315,615.0</t>
+  </si>
+  <si>
+    <t>81,297,887.59</t>
+  </si>
+  <si>
+    <t>49,084,593.9</t>
+  </si>
+  <si>
+    <t>43,352,141.9</t>
+  </si>
+  <si>
+    <t>29,497,592.7</t>
+  </si>
+  <si>
+    <t>19,677,209.2</t>
+  </si>
+  <si>
+    <t>22,075,081.0</t>
+  </si>
+  <si>
+    <t>8,579,281.19</t>
+  </si>
+  <si>
+    <t>1,840,806.5</t>
+  </si>
+  <si>
+    <t>241,078,208.4</t>
+  </si>
+  <si>
+    <t>50,638,603.0</t>
+  </si>
+  <si>
+    <t>27,644,206.0</t>
+  </si>
+  <si>
+    <t>20,768,616.0</t>
+  </si>
+  <si>
+    <t>15,371,253.0</t>
+  </si>
+  <si>
+    <t>50,350,997.3</t>
+  </si>
+  <si>
+    <t>49,447,200.0</t>
+  </si>
+  <si>
+    <t>33,741,972.29</t>
+  </si>
+  <si>
+    <t>6,803,097.6</t>
+  </si>
+  <si>
+    <t>4,760,225.0</t>
   </si>
 </sst>
 </file>
@@ -1675,7 +1657,7 @@
         <v>55</v>
       </c>
       <c r="D9" s="10">
-        <v>0.02529701180058931</v>
+        <v>0.6504700535526896</v>
       </c>
       <c r="E9" s="11" t="s">
         <v>64</v>
@@ -1684,52 +1666,52 @@
         <v>65</v>
       </c>
       <c r="G9" s="12">
-        <v>0.04488568770969287</v>
+        <v>0.1182893528732227</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="J9" s="14">
-        <v>0.06312087573960157</v>
+        <v>0.1470933080153174</v>
       </c>
       <c r="K9" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="L9" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="L9" s="15" t="s">
-        <v>84</v>
-      </c>
       <c r="M9" s="16">
-        <v>0.3579001869333949</v>
+        <v>0.08570560366887471</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="O9" s="17" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="P9" s="18">
-        <v>0.07860607658070967</v>
+        <v>0.0754817283348498</v>
       </c>
       <c r="Q9" s="15" t="s">
-        <v>62</v>
+        <v>91</v>
       </c>
       <c r="R9" s="15" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="S9" s="16">
-        <v>0.04518644360383732</v>
+        <v>0.03692670495564958</v>
       </c>
       <c r="T9" s="17" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="U9" s="17" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="V9" s="18">
-        <v>0.02062798634077263</v>
+        <v>0.4846621701832204</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -1741,61 +1723,61 @@
         <v>57</v>
       </c>
       <c r="D10" s="10">
-        <v>0.02285195117637303</v>
+        <v>0.1185317550067032</v>
       </c>
       <c r="E10" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="F10" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="F10" s="11" t="s">
+      <c r="G10" s="12">
+        <v>0.0641722597929994</v>
+      </c>
+      <c r="H10" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="I10" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="J10" s="14">
+        <v>0.04338035182065619</v>
+      </c>
+      <c r="K10" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="L10" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="M10" s="16">
+        <v>0.07222730711963291</v>
+      </c>
+      <c r="N10" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="O10" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="P10" s="18">
+        <v>0.03562160444200743</v>
+      </c>
+      <c r="Q10" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="R10" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="S10" s="16">
+        <v>0.03473186848902934</v>
+      </c>
+      <c r="T10" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="G10" s="12">
-        <v>0.02586885363628522</v>
-      </c>
-      <c r="H10" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="I10" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="J10" s="14">
-        <v>0.02690224497416558</v>
-      </c>
-      <c r="K10" s="15" t="s">
-        <v>85</v>
-      </c>
-      <c r="L10" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="M10" s="16">
-        <v>0.08424901828089705</v>
-      </c>
-      <c r="N10" s="17" t="s">
-        <v>95</v>
-      </c>
-      <c r="O10" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="P10" s="18">
-        <v>0.04594306397081815</v>
-      </c>
-      <c r="Q10" s="15" t="s">
-        <v>104</v>
-      </c>
-      <c r="R10" s="15" t="s">
-        <v>105</v>
-      </c>
-      <c r="S10" s="16">
-        <v>0.03685531021648616</v>
-      </c>
-      <c r="T10" s="17" t="s">
-        <v>114</v>
-      </c>
       <c r="U10" s="17" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="V10" s="18">
-        <v>0.01468332630891759</v>
+        <v>0.01162821540138949</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -1807,61 +1789,61 @@
         <v>59</v>
       </c>
       <c r="D11" s="10">
-        <v>0.01778972531164986</v>
+        <v>0.02605254615843267</v>
       </c>
       <c r="E11" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="F11" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="F11" s="11" t="s">
-        <v>69</v>
-      </c>
       <c r="G11" s="12">
-        <v>0.01883079252510887</v>
+        <v>0.04694032375794925</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="J11" s="14">
-        <v>0.0254038639081529</v>
+        <v>0.02818906936960446</v>
       </c>
       <c r="K11" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="L11" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="L11" s="15" t="s">
-        <v>88</v>
-      </c>
       <c r="M11" s="16">
-        <v>0.06432939208393124</v>
+        <v>0.04164208413211715</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>97</v>
+        <v>60</v>
       </c>
       <c r="O11" s="17" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="P11" s="18">
-        <v>0.03892017646922517</v>
+        <v>0.02282265598386415</v>
       </c>
       <c r="Q11" s="15" t="s">
-        <v>106</v>
+        <v>60</v>
       </c>
       <c r="R11" s="15" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="S11" s="16">
-        <v>0.01814540835634375</v>
+        <v>0.02423729315216103</v>
       </c>
       <c r="T11" s="17" t="s">
-        <v>60</v>
+        <v>109</v>
       </c>
       <c r="U11" s="17" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="V11" s="18">
-        <v>0.01457559994792535</v>
+        <v>0.009060946330944267</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -1873,61 +1855,61 @@
         <v>61</v>
       </c>
       <c r="D12" s="10">
-        <v>0.01680899150763557</v>
+        <v>0.02336846430100383</v>
       </c>
       <c r="E12" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="F12" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="F12" s="11" t="s">
-        <v>71</v>
-      </c>
       <c r="G12" s="12">
-        <v>0.01878543086324036</v>
+        <v>0.03299226657710764</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="J12" s="14">
-        <v>0.02469395803757729</v>
+        <v>0.02696865380801923</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>89</v>
+        <v>64</v>
       </c>
       <c r="L12" s="15" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="M12" s="16">
-        <v>0.02438985564546832</v>
+        <v>0.04016418070789829</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>99</v>
+        <v>64</v>
       </c>
       <c r="O12" s="17" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="P12" s="18">
-        <v>0.03889817447666308</v>
+        <v>0.01090072228637633</v>
       </c>
       <c r="Q12" s="15" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="R12" s="15" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="S12" s="16">
-        <v>0.01777053484615408</v>
+        <v>0.01386839239018576</v>
       </c>
       <c r="T12" s="17" t="s">
-        <v>117</v>
+        <v>60</v>
       </c>
       <c r="U12" s="17" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="V12" s="18">
-        <v>0.01302566024176553</v>
+        <v>0.007917623857843661</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -1939,61 +1921,61 @@
         <v>63</v>
       </c>
       <c r="D13" s="10">
-        <v>0.0156360360367242</v>
+        <v>0.02095405653705676</v>
       </c>
       <c r="E13" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="F13" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="F13" s="11" t="s">
-        <v>73</v>
-      </c>
       <c r="G13" s="12">
-        <v>0.01860882690334453</v>
+        <v>0.01053584615249382</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J13" s="14">
-        <v>0.02182861622169178</v>
+        <v>0.01864986016472456</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="L13" s="15" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="M13" s="16">
-        <v>0.02183968098882985</v>
+        <v>0.03715466682190342</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="O13" s="17" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="P13" s="18">
-        <v>0.01470330794807158</v>
+        <v>0.006852886920751547</v>
       </c>
       <c r="Q13" s="15" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="R13" s="15" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="S13" s="16">
-        <v>0.01715203615540777</v>
+        <v>0.01326620216251345</v>
       </c>
       <c r="T13" s="17" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="U13" s="17" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="V13" s="18">
-        <v>0.012774687070629</v>
+        <v>0.006381042782072549</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -2004,7 +1986,7 @@
         <v>51</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>53</v>
@@ -2013,7 +1995,7 @@
         <v>51</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>53</v>
@@ -2022,7 +2004,7 @@
         <v>51</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>53</v>
@@ -2031,7 +2013,7 @@
         <v>51</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="M15" s="5" t="s">
         <v>53</v>
@@ -2040,7 +2022,7 @@
         <v>51</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="P15" s="6" t="s">
         <v>53</v>
@@ -2049,7 +2031,7 @@
         <v>51</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="S15" s="5" t="s">
         <v>53</v>
@@ -2058,7 +2040,7 @@
         <v>51</v>
       </c>
       <c r="U15" s="6" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="V15" s="6" t="s">
         <v>53</v>
@@ -2067,566 +2049,566 @@
     <row r="16" spans="1:22">
       <c r="A16" s="1"/>
       <c r="B16" s="9" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C16" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="D16" s="10">
+        <v>0.03208289061866753</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="F16" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="D16" s="10">
-        <v>0.05438261465778178</v>
-      </c>
-      <c r="E16" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="F16" s="11" t="s">
+      <c r="G16" s="12">
+        <v>0.4237508280234905</v>
+      </c>
+      <c r="H16" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="I16" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="G16" s="12">
-        <v>0.1581050935787222</v>
-      </c>
-      <c r="H16" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="I16" s="13" t="s">
+      <c r="J16" s="14">
+        <v>0.3596733352271209</v>
+      </c>
+      <c r="K16" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="J16" s="14">
-        <v>0.02498809910634697</v>
-      </c>
-      <c r="K16" s="15" t="s">
-        <v>142</v>
-      </c>
       <c r="L16" s="15" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="M16" s="16">
-        <v>0.03360580471491868</v>
+        <v>0.1301778476745402</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="O16" s="17" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="P16" s="18">
-        <v>0.02556997264332405</v>
+        <v>0.4249483974149166</v>
       </c>
       <c r="Q16" s="15" t="s">
-        <v>124</v>
+        <v>54</v>
       </c>
       <c r="R16" s="15" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="S16" s="16">
-        <v>0.137164312766736</v>
+        <v>0.4960878967752965</v>
       </c>
       <c r="T16" s="17" t="s">
-        <v>58</v>
+        <v>138</v>
       </c>
       <c r="U16" s="17" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="V16" s="18">
-        <v>0.07435839227398436</v>
+        <v>0.1370912614686263</v>
       </c>
     </row>
     <row r="17" spans="1:22">
       <c r="A17" s="1"/>
       <c r="B17" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="D17" s="10">
+        <v>0.01766139941109632</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="F17" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="C17" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="D17" s="10">
-        <v>0.04536392725785583</v>
-      </c>
-      <c r="E17" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="F17" s="11" t="s">
+      <c r="G17" s="12">
+        <v>0.05326634404112121</v>
+      </c>
+      <c r="H17" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="G17" s="12">
-        <v>0.04623326866852787</v>
-      </c>
-      <c r="H17" s="13" t="s">
-        <v>137</v>
-      </c>
       <c r="I17" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="J17" s="14">
+        <v>0.06909130057146479</v>
+      </c>
+      <c r="K17" s="15" t="s">
         <v>138</v>
       </c>
-      <c r="J17" s="14">
-        <v>0.02478401847806698</v>
-      </c>
-      <c r="K17" s="15" t="s">
-        <v>144</v>
-      </c>
       <c r="L17" s="15" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="M17" s="16">
-        <v>0.0273488391712909</v>
+        <v>0.08099377440476173</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>70</v>
+        <v>146</v>
       </c>
       <c r="O17" s="17" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="P17" s="18">
-        <v>0.01728101215054954</v>
+        <v>0.321123845838051</v>
       </c>
       <c r="Q17" s="15" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="R17" s="15" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="S17" s="16">
-        <v>0.06929933872504904</v>
+        <v>0.08343490561786401</v>
       </c>
       <c r="T17" s="17" t="s">
-        <v>165</v>
+        <v>91</v>
       </c>
       <c r="U17" s="17" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="V17" s="18">
-        <v>0.03934873129514355</v>
+        <v>0.1046572699656809</v>
       </c>
     </row>
     <row r="18" spans="1:22">
       <c r="A18" s="1"/>
       <c r="B18" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="D18" s="10">
+        <v>0.01667262575701411</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="F18" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="C18" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="D18" s="10">
-        <v>0.02435854400121729</v>
-      </c>
-      <c r="E18" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="F18" s="11" t="s">
-        <v>131</v>
-      </c>
       <c r="G18" s="12">
-        <v>0.01310725286434629</v>
+        <v>0.05126435356716915</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>85</v>
+        <v>127</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="J18" s="14">
-        <v>0.02230839643481642</v>
+        <v>0.05469517205195652</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>91</v>
+        <v>58</v>
       </c>
       <c r="L18" s="15" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="M18" s="16">
-        <v>0.02060562006706113</v>
+        <v>0.0419525713201313</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>101</v>
+        <v>148</v>
       </c>
       <c r="O18" s="17" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="P18" s="18">
-        <v>0.01680571119301344</v>
+        <v>0.02550469312802136</v>
       </c>
       <c r="Q18" s="15" t="s">
-        <v>106</v>
+        <v>157</v>
       </c>
       <c r="R18" s="15" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="S18" s="16">
-        <v>0.04880554948123587</v>
+        <v>0.02700934048744291</v>
       </c>
       <c r="T18" s="17" t="s">
-        <v>106</v>
+        <v>163</v>
       </c>
       <c r="U18" s="17" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="V18" s="18">
-        <v>0.03205311219847172</v>
+        <v>0.08315752626727438</v>
       </c>
     </row>
     <row r="19" spans="1:22">
       <c r="A19" s="1"/>
       <c r="B19" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="D19" s="10">
+        <v>0.009842497409378963</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="F19" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="C19" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="D19" s="10">
-        <v>0.0219613493137902</v>
-      </c>
-      <c r="E19" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="F19" s="11" t="s">
-        <v>132</v>
-      </c>
       <c r="G19" s="12">
-        <v>0.01303244671090148</v>
+        <v>0.03407550008917475</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>83</v>
+        <v>133</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="J19" s="14">
-        <v>0.01612779835077011</v>
+        <v>0.02375930393691175</v>
       </c>
       <c r="K19" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="L19" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="M19" s="16">
+        <v>0.03241575137915966</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>150</v>
+      </c>
+      <c r="O19" s="17" t="s">
+        <v>151</v>
+      </c>
+      <c r="P19" s="18">
+        <v>0.00625038484321156</v>
+      </c>
+      <c r="Q19" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="L19" s="15" t="s">
-        <v>147</v>
-      </c>
-      <c r="M19" s="16">
-        <v>0.01123546548118468</v>
-      </c>
-      <c r="N19" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="O19" s="17" t="s">
-        <v>155</v>
-      </c>
-      <c r="P19" s="18">
-        <v>0.01252803651337537</v>
-      </c>
-      <c r="Q19" s="15" t="s">
-        <v>60</v>
-      </c>
       <c r="R19" s="15" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="S19" s="16">
-        <v>0.02966128397047652</v>
+        <v>0.02540776162414944</v>
       </c>
       <c r="T19" s="17" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="U19" s="17" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="V19" s="18">
-        <v>0.02999540464341532</v>
+        <v>0.01039358212145215</v>
       </c>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="1"/>
       <c r="B20" s="9" t="s">
-        <v>83</v>
+        <v>112</v>
       </c>
       <c r="C20" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="D20" s="10">
+        <v>0.007878244401124671</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="F20" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="D20" s="10">
-        <v>0.01941972772105119</v>
-      </c>
-      <c r="E20" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="F20" s="11" t="s">
-        <v>134</v>
-      </c>
       <c r="G20" s="12">
-        <v>0.008871247791714519</v>
+        <v>0.01275777697881515</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="J20" s="14">
-        <v>0.01378443060787158</v>
+        <v>0.02064651054714886</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="L20" s="15" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="M20" s="16">
-        <v>0.009298490294809376</v>
+        <v>0.02044352094467317</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>58</v>
+        <v>152</v>
       </c>
       <c r="O20" s="17" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="P20" s="18">
-        <v>0.01221492056881074</v>
+        <v>0.004396434098104411</v>
       </c>
       <c r="Q20" s="15" t="s">
-        <v>162</v>
+        <v>136</v>
       </c>
       <c r="R20" s="15" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="S20" s="16">
-        <v>0.01727961550125244</v>
+        <v>0.01905840077851938</v>
       </c>
       <c r="T20" s="17" t="s">
-        <v>54</v>
+        <v>166</v>
       </c>
       <c r="U20" s="17" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="V20" s="18">
-        <v>0.01696863581717278</v>
+        <v>0.009768080691354063</v>
       </c>
     </row>
     <row r="23" spans="1:22">
       <c r="B23" s="19" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="24" spans="1:22">
       <c r="B24" s="20" t="s">
-        <v>83</v>
+        <v>54</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="25" spans="1:22">
       <c r="B25" s="20" t="s">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="26" spans="1:22">
       <c r="B26" s="20" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="27" spans="1:22">
       <c r="B27" s="20" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="28" spans="1:22">
       <c r="B28" s="20" t="s">
-        <v>180</v>
+        <v>146</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="30" spans="1:22">
       <c r="B30" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="C30" s="19" t="s">
+        <v>171</v>
+      </c>
+      <c r="D30" s="19" t="s">
         <v>172</v>
-      </c>
-      <c r="C30" s="19" t="s">
-        <v>173</v>
-      </c>
-      <c r="D30" s="19" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="31" spans="1:22">
       <c r="B31" s="20" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C31" s="21" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="D31" s="22">
-        <v>0.2523104830628474</v>
+        <v>0.2300628520879037</v>
       </c>
     </row>
     <row r="32" spans="1:22">
       <c r="B32" s="20" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C32" s="21" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="D32" s="22">
-        <v>0.2364448876605085</v>
+        <v>0.1453776338997468</v>
       </c>
     </row>
     <row r="33" spans="2:4">
       <c r="B33" s="20" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C33" s="21" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="D33" s="22">
-        <v>0.2130888583843879</v>
+        <v>0.1313998538484508</v>
       </c>
     </row>
     <row r="34" spans="2:4">
       <c r="B34" s="20" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C34" s="21" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="D34" s="22">
-        <v>0.06302238471224796</v>
+        <v>0.1254657925945156</v>
       </c>
     </row>
     <row r="35" spans="2:4">
       <c r="B35" s="20" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C35" s="21" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="D35" s="22">
-        <v>0.06195183817921189</v>
+        <v>0.0889880309101527</v>
       </c>
     </row>
     <row r="36" spans="2:4">
       <c r="B36" s="20" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C36" s="21" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="D36" s="22">
-        <v>0.03949356202355205</v>
+        <v>0.08364158266684991</v>
       </c>
     </row>
     <row r="37" spans="2:4">
       <c r="B37" s="20" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C37" s="21" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="D37" s="22">
-        <v>0.03685121148732112</v>
+        <v>0.07211664960069356</v>
       </c>
     </row>
     <row r="38" spans="2:4">
       <c r="B38" s="20" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C38" s="21" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="D38" s="22">
-        <v>0.02953223101380104</v>
+        <v>0.02974995266770654</v>
       </c>
     </row>
     <row r="39" spans="2:4">
       <c r="B39" s="20" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C39" s="21" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="D39" s="22">
-        <v>0.01500177950786998</v>
+        <v>0.01930604224885294</v>
       </c>
     </row>
     <row r="40" spans="2:4">
       <c r="B40" s="20" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="C40" s="21" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="D40" s="22">
-        <v>0.01424750213628967</v>
+        <v>0.01413985476053546</v>
       </c>
     </row>
     <row r="41" spans="2:4">
       <c r="B41" s="20" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="C41" s="21" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="D41" s="22">
-        <v>0.01385729409800174</v>
+        <v>0.004609674913624373</v>
       </c>
     </row>
     <row r="42" spans="2:4">
       <c r="B42" s="20" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C42" s="21" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="D42" s="22">
-        <v>0.006495083294503681</v>
+        <v>0.003299210083862153</v>
       </c>
     </row>
     <row r="43" spans="2:4">
       <c r="B43" s="20" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="C43" s="21" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="D43" s="22">
-        <v>0.005009994199425819</v>
+        <v>0.002026969449046062</v>
       </c>
     </row>
     <row r="44" spans="2:4">
       <c r="B44" s="20" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C44" s="21" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D44" s="22">
-        <v>0.001801407105599467</v>
+        <v>0.000463501528494229</v>
       </c>
     </row>
     <row r="45" spans="2:4">
       <c r="B45" s="20" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C45" s="21" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="D45" s="22">
-        <v>0.0001483881754907899</v>
+        <v>2.063063667417439E-05</v>
       </c>
     </row>
     <row r="46" spans="2:4">
       <c r="B46" s="20" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C46" s="20" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="D46" s="20" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
     </row>
   </sheetData>
@@ -3005,331 +2987,331 @@
     <row r="9" spans="1:22">
       <c r="A9" s="1"/>
       <c r="B9" s="9" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D9" s="10">
-        <v>0.1684628213817445</v>
+        <v>0.8027910775171649</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="G9" s="12">
-        <v>0.1352419777352382</v>
+        <v>0.1626389155993241</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="J9" s="14">
-        <v>0.1974499906353299</v>
+        <v>0.1604426458204456</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="M9" s="16">
-        <v>0.5303472182217277</v>
+        <v>0.1562392365639012</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="O9" s="17" t="s">
+        <v>231</v>
+      </c>
+      <c r="P9" s="18">
+        <v>0.1172671446167488</v>
+      </c>
+      <c r="Q9" s="15" t="s">
+        <v>179</v>
+      </c>
+      <c r="R9" s="15" t="s">
         <v>235</v>
       </c>
-      <c r="P9" s="18">
-        <v>0.1511292426896421</v>
-      </c>
-      <c r="Q9" s="15" t="s">
-        <v>184</v>
-      </c>
-      <c r="R9" s="15" t="s">
-        <v>239</v>
-      </c>
       <c r="S9" s="16">
-        <v>0.1157264439313151</v>
+        <v>0.05508300564307848</v>
       </c>
       <c r="T9" s="17" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="U9" s="17" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="V9" s="18">
-        <v>0.09702708403951464</v>
+        <v>0.4857756780491559</v>
       </c>
     </row>
     <row r="10" spans="1:22">
       <c r="A10" s="1"/>
       <c r="B10" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="D10" s="10">
-        <v>0.1385073295207333</v>
+        <v>0.03150279257496462</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="G10" s="12">
-        <v>0.1191480956499953</v>
+        <v>0.06513238184579097</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="J10" s="14">
-        <v>0.1329529295478139</v>
+        <v>0.08149974287699031</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="M10" s="16">
-        <v>0.08550835169222205</v>
+        <v>0.09576285076653149</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="O10" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="P10" s="18">
+        <v>0.02282265598386415</v>
+      </c>
+      <c r="Q10" s="15" t="s">
+        <v>187</v>
+      </c>
+      <c r="R10" s="15" t="s">
         <v>236</v>
       </c>
-      <c r="P10" s="18">
-        <v>0.1359034784596401</v>
-      </c>
-      <c r="Q10" s="15" t="s">
-        <v>182</v>
-      </c>
-      <c r="R10" s="15" t="s">
-        <v>240</v>
-      </c>
       <c r="S10" s="16">
-        <v>0.1102494446794187</v>
+        <v>0.04953337502290937</v>
       </c>
       <c r="T10" s="17" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="U10" s="17" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="V10" s="18">
-        <v>0.0945146481161511</v>
+        <v>0.02269413781204551</v>
       </c>
     </row>
     <row r="11" spans="1:22">
       <c r="A11" s="1"/>
       <c r="B11" s="9" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>217</v>
+        <v>61</v>
       </c>
       <c r="D11" s="10">
-        <v>0.08179329026112173</v>
+        <v>0.02336846430100383</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="G11" s="12">
-        <v>0.08248330873695471</v>
+        <v>0.06428745211027773</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="J11" s="14">
-        <v>0.06308449813233628</v>
+        <v>0.05758110856994158</v>
       </c>
       <c r="K11" s="15" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="L11" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="M11" s="16">
+        <v>0.08710489673387037</v>
+      </c>
+      <c r="N11" s="17" t="s">
+        <v>185</v>
+      </c>
+      <c r="O11" s="17" t="s">
         <v>232</v>
       </c>
-      <c r="M11" s="16">
-        <v>0.06259044609073744</v>
-      </c>
-      <c r="N11" s="17" t="s">
-        <v>204</v>
-      </c>
-      <c r="O11" s="17" t="s">
-        <v>94</v>
-      </c>
       <c r="P11" s="18">
-        <v>0.07860607658070967</v>
+        <v>0.01446468889150898</v>
       </c>
       <c r="Q11" s="15" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="R11" s="15" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="S11" s="16">
-        <v>0.04132728150977488</v>
+        <v>0.03386682909660605</v>
       </c>
       <c r="T11" s="17" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="U11" s="17" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="V11" s="18">
-        <v>0.09237004748001709</v>
+        <v>0.02197775356532867</v>
       </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1"/>
       <c r="B12" s="9" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="D12" s="10">
-        <v>0.03087325187307097</v>
+        <v>0.01226281528809087</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="G12" s="12">
-        <v>0.041173617298617</v>
+        <v>0.01589949307884133</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="J12" s="14">
-        <v>0.04785743079439248</v>
+        <v>0.0244073092107087</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="L12" s="15" t="s">
+        <v>229</v>
+      </c>
+      <c r="M12" s="16">
+        <v>0.08334979597123821</v>
+      </c>
+      <c r="N12" s="17" t="s">
+        <v>183</v>
+      </c>
+      <c r="O12" s="17" t="s">
         <v>233</v>
       </c>
-      <c r="M12" s="16">
-        <v>0.02637055700464436</v>
-      </c>
-      <c r="N12" s="17" t="s">
-        <v>186</v>
-      </c>
-      <c r="O12" s="17" t="s">
-        <v>237</v>
-      </c>
       <c r="P12" s="18">
-        <v>0.06668748907651592</v>
+        <v>0.01409234749548836</v>
       </c>
       <c r="Q12" s="15" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="R12" s="15" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="S12" s="16">
-        <v>0.03975117990249265</v>
+        <v>0.02432813192640289</v>
       </c>
       <c r="T12" s="17" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="U12" s="17" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="V12" s="18">
-        <v>0.03736616533263903</v>
+        <v>0.01973287907029687</v>
       </c>
     </row>
     <row r="13" spans="1:22">
       <c r="A13" s="1"/>
       <c r="B13" s="9" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="D13" s="10">
-        <v>0.02313260095174587</v>
+        <v>0.006993449591159225</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="G13" s="12">
-        <v>0.03909108852297138</v>
+        <v>0.01356724179425081</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="J13" s="14">
-        <v>0.03127927389957421</v>
+        <v>0.01196688096354211</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="L13" s="15" t="s">
+        <v>230</v>
+      </c>
+      <c r="M13" s="16">
+        <v>0.04845439172578529</v>
+      </c>
+      <c r="N13" s="17" t="s">
+        <v>181</v>
+      </c>
+      <c r="O13" s="17" t="s">
         <v>234</v>
       </c>
-      <c r="M13" s="16">
-        <v>0.01842181373103198</v>
-      </c>
-      <c r="N13" s="17" t="s">
-        <v>194</v>
-      </c>
-      <c r="O13" s="17" t="s">
-        <v>238</v>
-      </c>
       <c r="P13" s="18">
-        <v>0.03394871571627455</v>
+        <v>0.007183180213193961</v>
       </c>
       <c r="Q13" s="15" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="R13" s="15" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="S13" s="16">
-        <v>0.03933065710028193</v>
+        <v>0.02143687217362236</v>
       </c>
       <c r="T13" s="17" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="U13" s="17" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="V13" s="18">
-        <v>0.02665091183406411</v>
+        <v>0.01802489028220521</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -3340,7 +3322,7 @@
         <v>51</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>53</v>
@@ -3349,7 +3331,7 @@
         <v>51</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>53</v>
@@ -3358,7 +3340,7 @@
         <v>51</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>53</v>
@@ -3367,7 +3349,7 @@
         <v>51</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="M15" s="5" t="s">
         <v>53</v>
@@ -3376,7 +3358,7 @@
         <v>51</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="P15" s="6" t="s">
         <v>53</v>
@@ -3385,7 +3367,7 @@
         <v>51</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="S15" s="5" t="s">
         <v>53</v>
@@ -3394,7 +3376,7 @@
         <v>51</v>
       </c>
       <c r="U15" s="6" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="V15" s="6" t="s">
         <v>53</v>
@@ -3403,331 +3385,331 @@
     <row r="16" spans="1:22">
       <c r="A16" s="1"/>
       <c r="B16" s="9" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="D16" s="10">
-        <v>0.1583448770245772</v>
+        <v>0.05825742052771971</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="G16" s="12">
-        <v>0.2110771180262351</v>
+        <v>0.5450390573538056</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="J16" s="14">
-        <v>0.1148862693619737</v>
+        <v>0.3597144726196991</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="L16" s="15" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="M16" s="16">
-        <v>0.09883429303640776</v>
+        <v>0.1574917111886219</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="O16" s="17" t="s">
-        <v>269</v>
+        <v>145</v>
       </c>
       <c r="P16" s="18">
-        <v>0.120138693433199</v>
+        <v>0.4249483974149166</v>
       </c>
       <c r="Q16" s="15" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="R16" s="15" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="S16" s="16">
-        <v>0.1671695511341287</v>
+        <v>0.5239054772124152</v>
       </c>
       <c r="T16" s="17" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="U16" s="17" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="V16" s="18">
-        <v>0.1416779702643734</v>
+        <v>0.1403891485972722</v>
       </c>
     </row>
     <row r="17" spans="1:22">
       <c r="A17" s="1"/>
       <c r="B17" s="9" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="D17" s="10">
-        <v>0.1182615227952882</v>
+        <v>0.0203785044290211</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="G17" s="12">
-        <v>0.1380672491816945</v>
+        <v>0.04194739536562973</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="J17" s="14">
-        <v>0.1130136900984887</v>
+        <v>0.08751108171934577</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="L17" s="15" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="M17" s="16">
-        <v>0.05657546171172374</v>
+        <v>0.09508754673116002</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="O17" s="17" t="s">
-        <v>270</v>
+        <v>147</v>
       </c>
       <c r="P17" s="18">
-        <v>0.0805397880584636</v>
+        <v>0.321123845838051</v>
       </c>
       <c r="Q17" s="15" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="R17" s="15" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="S17" s="16">
-        <v>0.1576098405587158</v>
+        <v>0.1100466178430627</v>
       </c>
       <c r="T17" s="17" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="U17" s="17" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="V17" s="18">
-        <v>0.1140972809320795</v>
+        <v>0.1378691720276817</v>
       </c>
     </row>
     <row r="18" spans="1:22">
       <c r="A18" s="1"/>
       <c r="B18" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="D18" s="10">
-        <v>0.08821555710703743</v>
+        <v>0.01699082930180016</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="G18" s="12">
-        <v>0.08626095482775782</v>
+        <v>0.02664292329759781</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="J18" s="14">
-        <v>0.1019768752124996</v>
+        <v>0.08435258253924061</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="L18" s="15" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="M18" s="16">
-        <v>0.03249353783481791</v>
+        <v>0.0839825389451196</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="O18" s="17" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="P18" s="18">
-        <v>0.07779549067444319</v>
+        <v>0.04448415583025574</v>
       </c>
       <c r="Q18" s="15" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="R18" s="15" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="S18" s="16">
-        <v>0.1148443697952863</v>
+        <v>0.06007573655333466</v>
       </c>
       <c r="T18" s="17" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="U18" s="17" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="V18" s="18">
-        <v>0.08799696030245316</v>
+        <v>0.09407970084417255</v>
       </c>
     </row>
     <row r="19" spans="1:22">
       <c r="A19" s="1"/>
       <c r="B19" s="9" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="D19" s="10">
-        <v>0.03489248679043998</v>
+        <v>0.008080144678221249</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="G19" s="12">
-        <v>0.01722617035295749</v>
+        <v>0.0118963269361282</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="J19" s="14">
-        <v>0.02851277731497938</v>
+        <v>0.03039455762788099</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="L19" s="15" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="M19" s="16">
-        <v>0.01723483472457668</v>
+        <v>0.05714326026680185</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="O19" s="17" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="P19" s="18">
-        <v>0.0526468286920533</v>
+        <v>0.0172883660908145</v>
       </c>
       <c r="Q19" s="15" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="R19" s="15" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="S19" s="16">
-        <v>0.0627745302533389</v>
+        <v>0.04513386651052199</v>
       </c>
       <c r="T19" s="17" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="U19" s="17" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="V19" s="18">
-        <v>0.06934254743315187</v>
+        <v>0.01896846400474664</v>
       </c>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="1"/>
       <c r="B20" s="9" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="D20" s="10">
-        <v>0.02414517525434816</v>
+        <v>0.003767902064585219</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="G20" s="12">
-        <v>0.0148849225890416</v>
+        <v>0.01042003556451657</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="J20" s="14">
-        <v>0.02556478430031032</v>
+        <v>0.02098725306949783</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="L20" s="15" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="M20" s="16">
-        <v>0.01096570126752277</v>
+        <v>0.03811903900347461</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="O20" s="17" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="P20" s="18">
-        <v>0.03065983770166697</v>
+        <v>0.003709464223453933</v>
       </c>
       <c r="Q20" s="15" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="R20" s="15" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="S20" s="16">
-        <v>0.02874101969813071</v>
+        <v>0.03340444452348008</v>
       </c>
       <c r="T20" s="17" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="U20" s="17" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="V20" s="18">
-        <v>0.05910947613585649</v>
+        <v>0.01327250641928099</v>
       </c>
     </row>
   </sheetData>

--- a/Daily_Report/Top 7 broker List with its Turnover 2024-10-29.xlsx
+++ b/Daily_Report/Top 7 broker List with its Turnover 2024-10-29.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="282">
   <si>
     <t>Date: 2024-10-29</t>
   </si>
@@ -59,109 +59,109 @@
     <t>7</t>
   </si>
   <si>
+    <t>Naasa Securities Co. Ltd.</t>
+  </si>
+  <si>
+    <t>Dynamic Money Managers Securities Pvt.Ltd</t>
+  </si>
+  <si>
     <t>Linch Stock Market Limited</t>
   </si>
   <si>
-    <t>Online Securities Pvt.Ltd</t>
+    <t>Shree Krishna Securities Limited</t>
+  </si>
+  <si>
+    <t>Araya Tara Investment And Securities Pvt. Ltd.</t>
   </si>
   <si>
     <t>Sani Securities Company Limited</t>
   </si>
   <si>
-    <t>Naasa Securities Co. Ltd.</t>
-  </si>
-  <si>
-    <t>Kohinoor Investment and Securities Pvt.Ltd</t>
-  </si>
-  <si>
-    <t>Araya Tara Investment And Securities Pvt. Ltd.</t>
-  </si>
-  <si>
-    <t>ABC Securities Pvt. Limited</t>
+    <t>Vision Securities Pvt.Limited</t>
+  </si>
+  <si>
+    <t>58</t>
+  </si>
+  <si>
+    <t>44</t>
   </si>
   <si>
     <t>41</t>
   </si>
   <si>
-    <t>49</t>
+    <t>28</t>
+  </si>
+  <si>
+    <t>57</t>
   </si>
   <si>
     <t>42</t>
   </si>
   <si>
-    <t>58</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>57</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>903,620,354.68</t>
-  </si>
-  <si>
-    <t>701,149,190.4</t>
-  </si>
-  <si>
-    <t>586,814,051.33</t>
-  </si>
-  <si>
-    <t>516,204,230.6</t>
-  </si>
-  <si>
-    <t>496,245,923.7</t>
-  </si>
-  <si>
-    <t>460,155,922.93</t>
-  </si>
-  <si>
-    <t>358,653,056.9</t>
-  </si>
-  <si>
-    <t>798,651,138.08</t>
-  </si>
-  <si>
-    <t>239,925,507.7</t>
-  </si>
-  <si>
-    <t>212,052,318.1</t>
-  </si>
-  <si>
-    <t>280,633,798.39</t>
-  </si>
-  <si>
-    <t>89,224,056.2</t>
-  </si>
-  <si>
-    <t>88,651,511.04</t>
-  </si>
-  <si>
-    <t>209,883,985.9</t>
-  </si>
-  <si>
-    <t>104,969,216.6</t>
-  </si>
-  <si>
-    <t>461,223,682.7</t>
-  </si>
-  <si>
-    <t>374,761,733.23</t>
-  </si>
-  <si>
-    <t>235,570,432.2</t>
-  </si>
-  <si>
-    <t>407,021,867.5</t>
-  </si>
-  <si>
-    <t>371,504,411.9</t>
-  </si>
-  <si>
-    <t>148,769,071.0</t>
+    <t>34</t>
+  </si>
+  <si>
+    <t>1,620,467,280.5</t>
+  </si>
+  <si>
+    <t>946,789,598.5</t>
+  </si>
+  <si>
+    <t>875,340,760.88</t>
+  </si>
+  <si>
+    <t>630,106,654.1</t>
+  </si>
+  <si>
+    <t>605,162,128.9</t>
+  </si>
+  <si>
+    <t>581,631,100.79</t>
+  </si>
+  <si>
+    <t>537,355,186.09</t>
+  </si>
+  <si>
+    <t>667,861,088.7</t>
+  </si>
+  <si>
+    <t>536,485,814.7</t>
+  </si>
+  <si>
+    <t>502,536,305.48</t>
+  </si>
+  <si>
+    <t>523,451,351.8</t>
+  </si>
+  <si>
+    <t>389,743,767.9</t>
+  </si>
+  <si>
+    <t>234,907,338.8</t>
+  </si>
+  <si>
+    <t>156,247,455.19</t>
+  </si>
+  <si>
+    <t>952,606,191.8</t>
+  </si>
+  <si>
+    <t>410,303,783.8</t>
+  </si>
+  <si>
+    <t>372,804,455.4</t>
+  </si>
+  <si>
+    <t>106,655,302.3</t>
+  </si>
+  <si>
+    <t>215,418,361.0</t>
+  </si>
+  <si>
+    <t>346,723,762.0</t>
+  </si>
+  <si>
+    <t>381,107,730.9</t>
   </si>
   <si>
     <t>Top 5 Buy</t>
@@ -179,346 +179,358 @@
     <t>% of turnover</t>
   </si>
   <si>
+    <t>MMKJL</t>
+  </si>
+  <si>
+    <t>271,316,782.0</t>
+  </si>
+  <si>
+    <t>MKCL</t>
+  </si>
+  <si>
+    <t>76,707,365.0</t>
+  </si>
+  <si>
+    <t>SKBBL</t>
+  </si>
+  <si>
+    <t>54,529,152.0</t>
+  </si>
+  <si>
+    <t>SANIMA</t>
+  </si>
+  <si>
+    <t>31,912,000.0</t>
+  </si>
+  <si>
+    <t>HIDCLP</t>
+  </si>
+  <si>
+    <t>30,451,200.0</t>
+  </si>
+  <si>
+    <t>NGPL</t>
+  </si>
+  <si>
+    <t>292,889,539.0</t>
+  </si>
+  <si>
+    <t>SJLIC</t>
+  </si>
+  <si>
+    <t>103,869,184.0</t>
+  </si>
+  <si>
+    <t>SPDL</t>
+  </si>
+  <si>
+    <t>103,005,012.0</t>
+  </si>
+  <si>
+    <t>UMRH</t>
+  </si>
+  <si>
+    <t>15,815,138.8</t>
+  </si>
+  <si>
+    <t>SHIVM</t>
+  </si>
+  <si>
+    <t>15,462,400.0</t>
+  </si>
+  <si>
+    <t>NFS</t>
+  </si>
+  <si>
+    <t>216,144,780.0</t>
+  </si>
+  <si>
+    <t>NMLBBL</t>
+  </si>
+  <si>
+    <t>132,147,672.0</t>
+  </si>
+  <si>
     <t>JFL</t>
   </si>
   <si>
-    <t>587,777,980.5</t>
+    <t>69,667,064.5</t>
   </si>
   <si>
     <t>SFCL</t>
   </si>
   <si>
-    <t>107,107,706.5</t>
-  </si>
-  <si>
-    <t>RNLI</t>
-  </si>
-  <si>
-    <t>23,541,611.0</t>
+    <t>33,411,635.5</t>
+  </si>
+  <si>
+    <t>RLFL</t>
+  </si>
+  <si>
+    <t>16,738,956.0</t>
+  </si>
+  <si>
+    <t>CZBIL</t>
+  </si>
+  <si>
+    <t>309,660,108.8</t>
+  </si>
+  <si>
+    <t>PCBL</t>
+  </si>
+  <si>
+    <t>172,659,200.0</t>
+  </si>
+  <si>
+    <t>CFCL</t>
+  </si>
+  <si>
+    <t>30,278,230.0</t>
+  </si>
+  <si>
+    <t>4,108,600.0</t>
+  </si>
+  <si>
+    <t>HRL</t>
+  </si>
+  <si>
+    <t>2,189,042.4</t>
+  </si>
+  <si>
+    <t>RHPL</t>
+  </si>
+  <si>
+    <t>243,520,000.0</t>
+  </si>
+  <si>
+    <t>43,321,270.0</t>
   </si>
   <si>
     <t>LICN</t>
   </si>
   <si>
-    <t>21,116,220.0</t>
-  </si>
-  <si>
-    <t>NFS</t>
-  </si>
-  <si>
-    <t>18,934,512.0</t>
-  </si>
-  <si>
-    <t>JBBL</t>
-  </si>
-  <si>
-    <t>82,938,484.0</t>
-  </si>
-  <si>
-    <t>44,994,328.0</t>
+    <t>36,034,560.0</t>
+  </si>
+  <si>
+    <t>SHINE</t>
+  </si>
+  <si>
+    <t>12,561,500.0</t>
+  </si>
+  <si>
+    <t>7,340,092.0</t>
+  </si>
+  <si>
+    <t>AKPL</t>
+  </si>
+  <si>
+    <t>71,600,128.0</t>
+  </si>
+  <si>
+    <t>SBL</t>
+  </si>
+  <si>
+    <t>57,753,395.9</t>
+  </si>
+  <si>
+    <t>MBL</t>
+  </si>
+  <si>
+    <t>39,240,717.2</t>
+  </si>
+  <si>
+    <t>PFL</t>
+  </si>
+  <si>
+    <t>12,795,570.0</t>
+  </si>
+  <si>
+    <t>8,885,160.5</t>
+  </si>
+  <si>
+    <t>GFCL</t>
+  </si>
+  <si>
+    <t>46,576,080.0</t>
+  </si>
+  <si>
+    <t>KSBBL</t>
+  </si>
+  <si>
+    <t>29,440,000.0</t>
+  </si>
+  <si>
+    <t>HIDCL</t>
+  </si>
+  <si>
+    <t>25,889,526.0</t>
+  </si>
+  <si>
+    <t>NICA</t>
+  </si>
+  <si>
+    <t>11,533,234.2</t>
+  </si>
+  <si>
+    <t>8,976,550.0</t>
+  </si>
+  <si>
+    <t>Sell Amount</t>
+  </si>
+  <si>
+    <t>359,645,664.8</t>
+  </si>
+  <si>
+    <t>313,456,047.7</t>
+  </si>
+  <si>
+    <t>80,820,371.0</t>
+  </si>
+  <si>
+    <t>RADHI</t>
+  </si>
+  <si>
+    <t>51,439,744.0</t>
+  </si>
+  <si>
+    <t>BFC</t>
+  </si>
+  <si>
+    <t>26,161,792.0</t>
+  </si>
+  <si>
+    <t>196,841,598.0</t>
+  </si>
+  <si>
+    <t>BPCL</t>
+  </si>
+  <si>
+    <t>123,379,200.0</t>
+  </si>
+  <si>
+    <t>PRVU</t>
+  </si>
+  <si>
+    <t>48,155,800.0</t>
+  </si>
+  <si>
+    <t>30,916,203.0</t>
+  </si>
+  <si>
+    <t>DOLTI</t>
+  </si>
+  <si>
+    <t>2,342,400.0</t>
+  </si>
+  <si>
+    <t>298,487,538.0</t>
+  </si>
+  <si>
+    <t>29,557,055.0</t>
+  </si>
+  <si>
+    <t>IGI</t>
+  </si>
+  <si>
+    <t>21,271,330.0</t>
+  </si>
+  <si>
+    <t>SPIL</t>
+  </si>
+  <si>
+    <t>5,780,706.0</t>
+  </si>
+  <si>
+    <t>4,028,538.0</t>
+  </si>
+  <si>
+    <t>MSHL</t>
+  </si>
+  <si>
+    <t>60,537,984.0</t>
+  </si>
+  <si>
+    <t>10,310,400.0</t>
+  </si>
+  <si>
+    <t>9,292,800.0</t>
+  </si>
+  <si>
+    <t>HEI</t>
+  </si>
+  <si>
+    <t>8,678,400.0</t>
+  </si>
+  <si>
+    <t>7,796,480.0</t>
+  </si>
+  <si>
+    <t>TRH</t>
+  </si>
+  <si>
+    <t>68,425,299.0</t>
+  </si>
+  <si>
+    <t>MCHL</t>
+  </si>
+  <si>
+    <t>67,900,358.0</t>
+  </si>
+  <si>
+    <t>GHL</t>
+  </si>
+  <si>
+    <t>57,622,510.0</t>
+  </si>
+  <si>
+    <t>SSHL</t>
+  </si>
+  <si>
+    <t>5,726,720.0</t>
+  </si>
+  <si>
+    <t>1,693,467.0</t>
+  </si>
+  <si>
+    <t>276,815,292.0</t>
+  </si>
+  <si>
+    <t>GVL</t>
+  </si>
+  <si>
+    <t>27,696,870.0</t>
+  </si>
+  <si>
+    <t>6,504,960.0</t>
+  </si>
+  <si>
+    <t>SAPDBL</t>
+  </si>
+  <si>
+    <t>4,012,800.0</t>
+  </si>
+  <si>
+    <t>3,617,612.0</t>
+  </si>
+  <si>
+    <t>KRBL</t>
+  </si>
+  <si>
+    <t>130,011,000.0</t>
+  </si>
+  <si>
+    <t>77,314,598.4</t>
+  </si>
+  <si>
+    <t>51,806,295.5</t>
+  </si>
+  <si>
+    <t>45,386,203.0</t>
   </si>
   <si>
     <t>ICFC</t>
   </si>
   <si>
-    <t>32,912,170.0</t>
-  </si>
-  <si>
-    <t>EDBL</t>
-  </si>
-  <si>
-    <t>23,132,501.0</t>
-  </si>
-  <si>
-    <t>GMFIL</t>
-  </si>
-  <si>
-    <t>7,387,200.0</t>
-  </si>
-  <si>
-    <t>86,316,420.0</t>
-  </si>
-  <si>
-    <t>SPDL</t>
-  </si>
-  <si>
-    <t>25,456,200.0</t>
-  </si>
-  <si>
-    <t>PRSF</t>
-  </si>
-  <si>
-    <t>16,541,742.0</t>
-  </si>
-  <si>
-    <t>UPCL</t>
-  </si>
-  <si>
-    <t>15,825,585.0</t>
-  </si>
-  <si>
-    <t>MDB</t>
-  </si>
-  <si>
-    <t>10,944,000.0</t>
-  </si>
-  <si>
-    <t>IGI</t>
-  </si>
-  <si>
-    <t>44,241,595.2</t>
-  </si>
-  <si>
-    <t>AKJCL</t>
-  </si>
-  <si>
-    <t>37,284,041.5</t>
-  </si>
-  <si>
-    <t>SAPDBL</t>
-  </si>
-  <si>
-    <t>21,495,820.0</t>
-  </si>
-  <si>
-    <t>20,732,920.0</t>
-  </si>
-  <si>
-    <t>ULHC</t>
-  </si>
-  <si>
-    <t>19,179,396.2</t>
-  </si>
-  <si>
-    <t>BFC</t>
-  </si>
-  <si>
-    <t>37,457,500.0</t>
-  </si>
-  <si>
-    <t>17,677,076.0</t>
-  </si>
-  <si>
-    <t>11,325,650.0</t>
-  </si>
-  <si>
-    <t>5,409,439.0</t>
-  </si>
-  <si>
-    <t>SNLI</t>
-  </si>
-  <si>
-    <t>3,400,717.2</t>
-  </si>
-  <si>
-    <t>16,992,042.0</t>
-  </si>
-  <si>
-    <t>NIFRA</t>
-  </si>
-  <si>
-    <t>15,982,075.0</t>
-  </si>
-  <si>
-    <t>11,152,934.0</t>
-  </si>
-  <si>
-    <t>CHDC</t>
-  </si>
-  <si>
-    <t>6,381,622.9</t>
-  </si>
-  <si>
-    <t>SAHAS</t>
-  </si>
-  <si>
-    <t>6,104,521.5</t>
-  </si>
-  <si>
-    <t>PRVU</t>
-  </si>
-  <si>
-    <t>173,825,568.9</t>
-  </si>
-  <si>
-    <t>4,170,495.0</t>
-  </si>
-  <si>
-    <t>UNHPL</t>
-  </si>
-  <si>
-    <t>3,249,736.1</t>
-  </si>
-  <si>
-    <t>2,839,680.0</t>
-  </si>
-  <si>
-    <t>CFCL</t>
-  </si>
-  <si>
-    <t>2,288,580.5</t>
-  </si>
-  <si>
-    <t>Sell Amount</t>
-  </si>
-  <si>
-    <t>28,990,753.0</t>
-  </si>
-  <si>
-    <t>15,959,200.0</t>
-  </si>
-  <si>
-    <t>15,065,724.0</t>
-  </si>
-  <si>
-    <t>PFL</t>
-  </si>
-  <si>
-    <t>8,893,881.0</t>
-  </si>
-  <si>
-    <t>7,118,942.0</t>
-  </si>
-  <si>
-    <t>297,112,550.0</t>
-  </si>
-  <si>
-    <t>37,347,654.0</t>
-  </si>
-  <si>
-    <t>MFIL</t>
-  </si>
-  <si>
-    <t>35,943,960.0</t>
-  </si>
-  <si>
-    <t>KRBL</t>
-  </si>
-  <si>
-    <t>23,892,009.3</t>
-  </si>
-  <si>
-    <t>GBIME</t>
-  </si>
-  <si>
-    <t>8,945,105.0</t>
-  </si>
-  <si>
-    <t>211,061,367.0</t>
-  </si>
-  <si>
-    <t>FMDBL</t>
-  </si>
-  <si>
-    <t>40,543,746.0</t>
-  </si>
-  <si>
-    <t>32,095,895.5</t>
-  </si>
-  <si>
-    <t>SPC</t>
-  </si>
-  <si>
-    <t>13,942,293.4</t>
-  </si>
-  <si>
-    <t>12,115,662.5</t>
-  </si>
-  <si>
-    <t>NGPL</t>
-  </si>
-  <si>
-    <t>67,198,355.7</t>
-  </si>
-  <si>
-    <t>NRN</t>
-  </si>
-  <si>
-    <t>41,809,329.0</t>
-  </si>
-  <si>
-    <t>21,656,094.8</t>
-  </si>
-  <si>
-    <t>SWBBL</t>
-  </si>
-  <si>
-    <t>16,733,148.0</t>
-  </si>
-  <si>
-    <t>HRL</t>
-  </si>
-  <si>
-    <t>10,553,032.0</t>
-  </si>
-  <si>
-    <t>210,878,910.0</t>
-  </si>
-  <si>
-    <t>HIDCL</t>
-  </si>
-  <si>
-    <t>159,356,399.5</t>
-  </si>
-  <si>
-    <t>SHPC</t>
-  </si>
-  <si>
-    <t>12,656,600.0</t>
-  </si>
-  <si>
-    <t>MBJC</t>
-  </si>
-  <si>
-    <t>3,101,728.0</t>
-  </si>
-  <si>
-    <t>SGIC</t>
-  </si>
-  <si>
-    <t>2,181,712.5</t>
-  </si>
-  <si>
-    <t>228,277,784.0</t>
-  </si>
-  <si>
-    <t>SBI</t>
-  </si>
-  <si>
-    <t>38,393,066.0</t>
-  </si>
-  <si>
-    <t>HDHPC</t>
-  </si>
-  <si>
-    <t>12,428,508.0</t>
-  </si>
-  <si>
-    <t>11,691,532.0</t>
-  </si>
-  <si>
-    <t>8,769,836.0</t>
-  </si>
-  <si>
-    <t>49,168,200.0</t>
-  </si>
-  <si>
-    <t>37,535,649.8</t>
-  </si>
-  <si>
-    <t>MMKJL</t>
-  </si>
-  <si>
-    <t>29,824,701.0</t>
-  </si>
-  <si>
-    <t>3,727,690.0</t>
-  </si>
-  <si>
-    <t>PROFL</t>
-  </si>
-  <si>
-    <t>3,503,352.0</t>
+    <t>15,179,088.0</t>
   </si>
   <si>
     <t>Top Traded Stocks</t>
@@ -536,112 +548,109 @@
     <t>Percentage (%)</t>
   </si>
   <si>
-    <t>625,590,491.2</t>
-  </si>
-  <si>
-    <t>424,647,020.0</t>
-  </si>
-  <si>
-    <t>GRDBL</t>
-  </si>
-  <si>
-    <t>237,892,159.0</t>
-  </si>
-  <si>
-    <t>208,775,494.8</t>
-  </si>
-  <si>
-    <t>188,840,465.9</t>
+    <t>599,757,573.0</t>
+  </si>
+  <si>
+    <t>380,404,159.7</t>
+  </si>
+  <si>
+    <t>359,778,592.8</t>
+  </si>
+  <si>
+    <t>314,453,522.0</t>
+  </si>
+  <si>
+    <t>309,819,580.8</t>
+  </si>
+  <si>
+    <t>Promoter Shares/debenture</t>
+  </si>
+  <si>
+    <t>1,931,425,352.5</t>
+  </si>
+  <si>
+    <t>Hydro Power</t>
+  </si>
+  <si>
+    <t>1,895,096,642.8</t>
   </si>
   <si>
     <t>Finance</t>
   </si>
   <si>
-    <t>1,409,886,027.7</t>
-  </si>
-  <si>
-    <t>Hydro Power</t>
-  </si>
-  <si>
-    <t>890,912,604.6</t>
+    <t>1,424,130,712.1</t>
+  </si>
+  <si>
+    <t>Commercial Banks</t>
+  </si>
+  <si>
+    <t>913,347,050.7</t>
   </si>
   <si>
     <t>Development Banks</t>
   </si>
   <si>
-    <t>805,253,070.2</t>
-  </si>
-  <si>
-    <t>Promoter Shares/debenture</t>
-  </si>
-  <si>
-    <t>768,887,572.8</t>
+    <t>541,230,849.5</t>
+  </si>
+  <si>
+    <t>Non Life Insurance</t>
+  </si>
+  <si>
+    <t>193,806,936.1</t>
+  </si>
+  <si>
+    <t>Microfinance</t>
+  </si>
+  <si>
+    <t>175,129,668.5</t>
   </si>
   <si>
     <t>Investment</t>
   </si>
   <si>
-    <t>545,342,197.9</t>
-  </si>
-  <si>
-    <t>Commercial Banks</t>
-  </si>
-  <si>
-    <t>512,577,748.5</t>
+    <t>106,823,158.1</t>
+  </si>
+  <si>
+    <t>Manufacturing And Processing</t>
+  </si>
+  <si>
+    <t>91,336,623.4</t>
+  </si>
+  <si>
+    <t>Hotels And Tourism</t>
+  </si>
+  <si>
+    <t>79,620,290.3</t>
   </si>
   <si>
     <t>Life Insurance</t>
   </si>
   <si>
-    <t>441,949,909.4</t>
-  </si>
-  <si>
-    <t>Non Life Insurance</t>
-  </si>
-  <si>
-    <t>182,315,581.2</t>
-  </si>
-  <si>
-    <t>Microfinance</t>
-  </si>
-  <si>
-    <t>118,312,534.9</t>
-  </si>
-  <si>
-    <t>Manufacturing And Processing</t>
-  </si>
-  <si>
-    <t>86,652,771.1</t>
-  </si>
-  <si>
-    <t>Hotels And Tourism</t>
-  </si>
-  <si>
-    <t>28,249,307.5</t>
+    <t>53,915,472.1</t>
   </si>
   <si>
     <t>Others</t>
   </si>
   <si>
-    <t>20,218,432.3</t>
+    <t>48,591,567.6</t>
   </si>
   <si>
     <t>Mutual Fund</t>
   </si>
   <si>
-    <t>12,421,805.08</t>
+    <t>4,741,737.11</t>
   </si>
   <si>
     <t>Trading</t>
   </si>
   <si>
-    <t>2,840,460.0</t>
+    <t>1,029,165.0</t>
   </si>
   <si>
     <t>Tradings</t>
   </si>
   <si>
-    <t>126,430.0</t>
+    <t>84,020.0</t>
   </si>
   <si>
     <t>Total</t>
@@ -653,202 +662,205 @@
     <t>100%</t>
   </si>
   <si>
-    <t>725,418,358.2</t>
-  </si>
-  <si>
-    <t>28,466,564.6</t>
-  </si>
-  <si>
-    <t>11,080,929.5</t>
-  </si>
-  <si>
-    <t>6,319,423.4</t>
-  </si>
-  <si>
-    <t>114,034,144.0</t>
-  </si>
-  <si>
-    <t>45,667,516.8</t>
-  </si>
-  <si>
-    <t>45,075,095.0</t>
-  </si>
-  <si>
-    <t>11,147,916.7</t>
-  </si>
-  <si>
-    <t>9,512,660.6</t>
-  </si>
-  <si>
-    <t>94,149,999.0</t>
-  </si>
-  <si>
-    <t>47,825,194.3</t>
-  </si>
-  <si>
-    <t>33,789,403.6</t>
-  </si>
-  <si>
-    <t>14,322,552.0</t>
-  </si>
-  <si>
-    <t>7,022,333.9</t>
-  </si>
-  <si>
-    <t>80,651,354.9</t>
-  </si>
-  <si>
-    <t>49,433,188.7</t>
-  </si>
-  <si>
-    <t>44,963,916.2</t>
-  </si>
-  <si>
-    <t>43,025,517.3</t>
-  </si>
-  <si>
-    <t>25,012,362.0</t>
-  </si>
-  <si>
-    <t>58,193,342.5</t>
-  </si>
-  <si>
-    <t>7,178,042.9</t>
-  </si>
-  <si>
-    <t>6,993,270.0</t>
-  </si>
-  <si>
-    <t>3,564,623.9</t>
-  </si>
-  <si>
-    <t>25,346,771.3</t>
-  </si>
-  <si>
-    <t>22,793,075.9</t>
-  </si>
-  <si>
-    <t>15,584,022.0</t>
-  </si>
-  <si>
-    <t>11,194,734.0</t>
-  </si>
-  <si>
-    <t>9,864,303.69</t>
-  </si>
-  <si>
-    <t>174,224,931.9</t>
-  </si>
-  <si>
-    <t>8,139,321.9</t>
-  </si>
-  <si>
-    <t>7,882,388.5</t>
-  </si>
-  <si>
-    <t>7,077,257.4</t>
-  </si>
-  <si>
-    <t>6,464,682.0</t>
-  </si>
-  <si>
-    <t>52,642,591.0</t>
-  </si>
-  <si>
-    <t>18,414,431.39</t>
-  </si>
-  <si>
-    <t>15,353,259.2</t>
-  </si>
-  <si>
-    <t>7,301,383.2</t>
-  </si>
-  <si>
-    <t>3,404,753.0</t>
-  </si>
-  <si>
-    <t>382,153,693.8</t>
-  </si>
-  <si>
-    <t>29,411,382.3</t>
-  </si>
-  <si>
-    <t>18,680,664.1</t>
-  </si>
-  <si>
-    <t>8,341,100.0</t>
-  </si>
-  <si>
-    <t>7,305,999.5</t>
-  </si>
-  <si>
-    <t>211,085,507.0</t>
-  </si>
-  <si>
-    <t>51,352,732.4</t>
-  </si>
-  <si>
-    <t>49,499,280.7</t>
-  </si>
-  <si>
-    <t>17,835,953.5</t>
-  </si>
-  <si>
-    <t>12,315,615.0</t>
-  </si>
-  <si>
-    <t>81,297,887.59</t>
-  </si>
-  <si>
-    <t>49,084,593.9</t>
-  </si>
-  <si>
-    <t>43,352,141.9</t>
-  </si>
-  <si>
-    <t>29,497,592.7</t>
-  </si>
-  <si>
-    <t>19,677,209.2</t>
-  </si>
-  <si>
-    <t>22,075,081.0</t>
-  </si>
-  <si>
-    <t>8,579,281.19</t>
-  </si>
-  <si>
-    <t>1,840,806.5</t>
-  </si>
-  <si>
-    <t>241,078,208.4</t>
-  </si>
-  <si>
-    <t>50,638,603.0</t>
-  </si>
-  <si>
-    <t>27,644,206.0</t>
-  </si>
-  <si>
-    <t>20,768,616.0</t>
-  </si>
-  <si>
-    <t>15,371,253.0</t>
-  </si>
-  <si>
-    <t>50,350,997.3</t>
-  </si>
-  <si>
-    <t>49,447,200.0</t>
-  </si>
-  <si>
-    <t>33,741,972.29</t>
-  </si>
-  <si>
-    <t>6,803,097.6</t>
-  </si>
-  <si>
-    <t>4,760,225.0</t>
+    <t>407,333,125.5</t>
+  </si>
+  <si>
+    <t>75,857,452.59</t>
+  </si>
+  <si>
+    <t>69,891,143.0</t>
+  </si>
+  <si>
+    <t>56,289,620.0</t>
+  </si>
+  <si>
+    <t>36,972,540.5</t>
+  </si>
+  <si>
+    <t>411,989,118.8</t>
+  </si>
+  <si>
+    <t>104,866,429.4</t>
+  </si>
+  <si>
+    <t>2,549,651.0</t>
+  </si>
+  <si>
+    <t>663,147.0</t>
+  </si>
+  <si>
+    <t>353,537,450.9</t>
+  </si>
+  <si>
+    <t>139,538,729.4</t>
+  </si>
+  <si>
+    <t>3,451,605.0</t>
+  </si>
+  <si>
+    <t>1,633,628.5</t>
+  </si>
+  <si>
+    <t>1,626,700.0</t>
+  </si>
+  <si>
+    <t>484,436,444.3</t>
+  </si>
+  <si>
+    <t>30,415,232.3</t>
+  </si>
+  <si>
+    <t>4,426,390.0</t>
+  </si>
+  <si>
+    <t>2,257,672.4</t>
+  </si>
+  <si>
+    <t>985,525.6</t>
+  </si>
+  <si>
+    <t>256,193,763.7</t>
+  </si>
+  <si>
+    <t>53,293,157.0</t>
+  </si>
+  <si>
+    <t>19,666,780.0</t>
+  </si>
+  <si>
+    <t>16,275,888.5</t>
+  </si>
+  <si>
+    <t>104,019,351.8</t>
+  </si>
+  <si>
+    <t>75,770,892.59</t>
+  </si>
+  <si>
+    <t>25,752,811.7</t>
+  </si>
+  <si>
+    <t>16,849,146.1</t>
+  </si>
+  <si>
+    <t>7,379,409.0</t>
+  </si>
+  <si>
+    <t>65,211,773.9</t>
+  </si>
+  <si>
+    <t>29,637,099.0</t>
+  </si>
+  <si>
+    <t>26,077,159.0</t>
+  </si>
+  <si>
+    <t>17,351,245.5</t>
+  </si>
+  <si>
+    <t>5,224,590.4</t>
+  </si>
+  <si>
+    <t>731,021,885.3</t>
+  </si>
+  <si>
+    <t>89,360,889.4</t>
+  </si>
+  <si>
+    <t>71,354,478.09</t>
+  </si>
+  <si>
+    <t>31,003,701.5</t>
+  </si>
+  <si>
+    <t>10,307,853.19</t>
+  </si>
+  <si>
+    <t>322,083,833.3</t>
+  </si>
+  <si>
+    <t>48,417,600.0</t>
+  </si>
+  <si>
+    <t>35,690,841.79</t>
+  </si>
+  <si>
+    <t>1,761,105.7</t>
+  </si>
+  <si>
+    <t>1,556,837.0</t>
+  </si>
+  <si>
+    <t>307,623,892.5</t>
+  </si>
+  <si>
+    <t>30,444,611.2</t>
+  </si>
+  <si>
+    <t>21,560,770.0</t>
+  </si>
+  <si>
+    <t>6,773,160.7</t>
+  </si>
+  <si>
+    <t>3,774,112.6</t>
+  </si>
+  <si>
+    <t>70,813,450.8</t>
+  </si>
+  <si>
+    <t>20,506,960.0</t>
+  </si>
+  <si>
+    <t>8,773,572.0</t>
+  </si>
+  <si>
+    <t>3,332,881.5</t>
+  </si>
+  <si>
+    <t>1,558,380.0</t>
+  </si>
+  <si>
+    <t>73,242,893.09</t>
+  </si>
+  <si>
+    <t>68,516,799.0</t>
+  </si>
+  <si>
+    <t>65,828,565.8</t>
+  </si>
+  <si>
+    <t>5,387,808.6</t>
+  </si>
+  <si>
+    <t>289,913,279.39</t>
+  </si>
+  <si>
+    <t>31,861,028.0</t>
+  </si>
+  <si>
+    <t>10,479,822.5</t>
+  </si>
+  <si>
+    <t>4,879,909.0</t>
+  </si>
+  <si>
+    <t>4,443,450.5</t>
+  </si>
+  <si>
+    <t>130,354,588.0</t>
+  </si>
+  <si>
+    <t>116,787,911.1</t>
+  </si>
+  <si>
+    <t>77,411,184.4</t>
+  </si>
+  <si>
+    <t>17,010,815.8</t>
+  </si>
+  <si>
+    <t>15,430,146.5</t>
   </si>
 </sst>
 </file>
@@ -1657,7 +1669,7 @@
         <v>55</v>
       </c>
       <c r="D9" s="10">
-        <v>0.6504700535526896</v>
+        <v>0.167431200410467</v>
       </c>
       <c r="E9" s="11" t="s">
         <v>64</v>
@@ -1666,52 +1678,52 @@
         <v>65</v>
       </c>
       <c r="G9" s="12">
-        <v>0.1182893528732227</v>
+        <v>0.3093501866349454</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="J9" s="14">
-        <v>0.1470933080153174</v>
+        <v>0.2469264424322075</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="M9" s="16">
-        <v>0.08570560366887471</v>
+        <v>0.4914407851196187</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="O9" s="17" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="P9" s="18">
-        <v>0.0754817283348498</v>
+        <v>0.4024045596551869</v>
       </c>
       <c r="Q9" s="15" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="R9" s="15" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="S9" s="16">
-        <v>0.03692670495564958</v>
+        <v>0.1231023029915666</v>
       </c>
       <c r="T9" s="17" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="U9" s="17" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="V9" s="18">
-        <v>0.4846621701832204</v>
+        <v>0.08667652458709565</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -1723,61 +1735,61 @@
         <v>57</v>
       </c>
       <c r="D10" s="10">
-        <v>0.1185317550067032</v>
+        <v>0.04733657132301475</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G10" s="12">
-        <v>0.0641722597929994</v>
+        <v>0.1097067227656071</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="J10" s="14">
-        <v>0.04338035182065619</v>
+        <v>0.1509671180708516</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="M10" s="16">
-        <v>0.07222730711963291</v>
+        <v>0.2740158334728495</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>56</v>
+        <v>88</v>
       </c>
       <c r="O10" s="17" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="P10" s="18">
-        <v>0.03562160444200743</v>
+        <v>0.07158622116480559</v>
       </c>
       <c r="Q10" s="15" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="R10" s="15" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="S10" s="16">
-        <v>0.03473186848902934</v>
+        <v>0.09929557724915937</v>
       </c>
       <c r="T10" s="17" t="s">
-        <v>67</v>
+        <v>112</v>
       </c>
       <c r="U10" s="17" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="V10" s="18">
-        <v>0.01162821540138949</v>
+        <v>0.05478685376365069</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -1789,61 +1801,61 @@
         <v>59</v>
       </c>
       <c r="D11" s="10">
-        <v>0.02605254615843267</v>
+        <v>0.0336502641282426</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G11" s="12">
-        <v>0.04694032375794925</v>
+        <v>0.1087939835452259</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J11" s="14">
-        <v>0.02818906936960446</v>
+        <v>0.07958850725740467</v>
       </c>
       <c r="K11" s="15" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L11" s="15" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="M11" s="16">
-        <v>0.04164208413211715</v>
+        <v>0.048052547617113</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>60</v>
+        <v>96</v>
       </c>
       <c r="O11" s="17" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="P11" s="18">
-        <v>0.02282265598386415</v>
+        <v>0.05954529915065872</v>
       </c>
       <c r="Q11" s="15" t="s">
-        <v>60</v>
+        <v>105</v>
       </c>
       <c r="R11" s="15" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="S11" s="16">
-        <v>0.02423729315216103</v>
+        <v>0.06746667629366219</v>
       </c>
       <c r="T11" s="17" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="U11" s="17" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="V11" s="18">
-        <v>0.009060946330944267</v>
+        <v>0.04817954059008942</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -1855,61 +1867,61 @@
         <v>61</v>
       </c>
       <c r="D12" s="10">
-        <v>0.02336846430100383</v>
+        <v>0.01969308506503967</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G12" s="12">
-        <v>0.03299226657710764</v>
+        <v>0.01670396339910783</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="J12" s="14">
-        <v>0.02696865380801923</v>
+        <v>0.03816986137651184</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="L12" s="15" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="M12" s="16">
-        <v>0.04016418070789829</v>
+        <v>0.006520483434456719</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>64</v>
+        <v>98</v>
       </c>
       <c r="O12" s="17" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="P12" s="18">
-        <v>0.01090072228637633</v>
+        <v>0.02075724735589943</v>
       </c>
       <c r="Q12" s="15" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="R12" s="15" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="S12" s="16">
-        <v>0.01386839239018576</v>
+        <v>0.0219994597647898</v>
       </c>
       <c r="T12" s="17" t="s">
-        <v>60</v>
+        <v>116</v>
       </c>
       <c r="U12" s="17" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="V12" s="18">
-        <v>0.007917623857843661</v>
+        <v>0.02146296248428447</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -1921,61 +1933,61 @@
         <v>63</v>
       </c>
       <c r="D13" s="10">
-        <v>0.02095405653705676</v>
+        <v>0.0187916166937997</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G13" s="12">
-        <v>0.01053584615249382</v>
+        <v>0.01633140037078681</v>
       </c>
       <c r="H13" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="I13" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="J13" s="14">
+        <v>0.01912278823069081</v>
+      </c>
+      <c r="K13" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="L13" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="M13" s="16">
+        <v>0.003474082341070773</v>
+      </c>
+      <c r="N13" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="I13" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="J13" s="14">
-        <v>0.01864986016472456</v>
-      </c>
-      <c r="K13" s="15" t="s">
-        <v>89</v>
-      </c>
-      <c r="L13" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="M13" s="16">
-        <v>0.03715466682190342</v>
-      </c>
-      <c r="N13" s="17" t="s">
-        <v>96</v>
-      </c>
       <c r="O13" s="17" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="P13" s="18">
-        <v>0.006852886920751547</v>
+        <v>0.01212913308594185</v>
       </c>
       <c r="Q13" s="15" t="s">
-        <v>104</v>
+        <v>56</v>
       </c>
       <c r="R13" s="15" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="S13" s="16">
-        <v>0.01326620216251345</v>
+        <v>0.01527628162898953</v>
       </c>
       <c r="T13" s="17" t="s">
-        <v>112</v>
+        <v>88</v>
       </c>
       <c r="U13" s="17" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="V13" s="18">
-        <v>0.006381042782072549</v>
+        <v>0.01670505883668813</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -1986,7 +1998,7 @@
         <v>51</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>53</v>
@@ -1995,7 +2007,7 @@
         <v>51</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>53</v>
@@ -2004,7 +2016,7 @@
         <v>51</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>53</v>
@@ -2013,7 +2025,7 @@
         <v>51</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="M15" s="5" t="s">
         <v>53</v>
@@ -2022,7 +2034,7 @@
         <v>51</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="P15" s="6" t="s">
         <v>53</v>
@@ -2031,7 +2043,7 @@
         <v>51</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="S15" s="5" t="s">
         <v>53</v>
@@ -2040,7 +2052,7 @@
         <v>51</v>
       </c>
       <c r="U15" s="6" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="V15" s="6" t="s">
         <v>53</v>
@@ -2049,566 +2061,566 @@
     <row r="16" spans="1:22">
       <c r="A16" s="1"/>
       <c r="B16" s="9" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D16" s="10">
-        <v>0.03208289061866753</v>
+        <v>0.2219394795117556</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="G16" s="12">
-        <v>0.4237508280234905</v>
+        <v>0.2079042675498932</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>60</v>
+        <v>107</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="J16" s="14">
-        <v>0.3596733352271209</v>
+        <v>0.3409958171031858</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="L16" s="15" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="M16" s="16">
-        <v>0.1301778476745402</v>
+        <v>0.09607577321408896</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>60</v>
+        <v>149</v>
       </c>
       <c r="O16" s="17" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="P16" s="18">
-        <v>0.4249483974149166</v>
+        <v>0.1130693672526671</v>
       </c>
       <c r="Q16" s="15" t="s">
         <v>54</v>
       </c>
       <c r="R16" s="15" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="S16" s="16">
-        <v>0.4960878967752965</v>
+        <v>0.4759293160548956</v>
       </c>
       <c r="T16" s="17" t="s">
-        <v>138</v>
+        <v>165</v>
       </c>
       <c r="U16" s="17" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="V16" s="18">
-        <v>0.1370912614686263</v>
+        <v>0.241946115647622</v>
       </c>
     </row>
     <row r="17" spans="1:22">
       <c r="A17" s="1"/>
       <c r="B17" s="9" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="C17" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="D17" s="10">
+        <v>0.1934355919875668</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="G17" s="12">
+        <v>0.1303132186870978</v>
+      </c>
+      <c r="H17" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="I17" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="J17" s="14">
+        <v>0.0337663414306054</v>
+      </c>
+      <c r="K17" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="D17" s="10">
-        <v>0.01766139941109632</v>
-      </c>
-      <c r="E17" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="F17" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="G17" s="12">
-        <v>0.05326634404112121</v>
-      </c>
-      <c r="H17" s="13" t="s">
-        <v>130</v>
-      </c>
-      <c r="I17" s="13" t="s">
-        <v>131</v>
-      </c>
-      <c r="J17" s="14">
-        <v>0.06909130057146479</v>
-      </c>
-      <c r="K17" s="15" t="s">
-        <v>138</v>
-      </c>
       <c r="L17" s="15" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="M17" s="16">
-        <v>0.08099377440476173</v>
+        <v>0.01636294416653424</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="O17" s="17" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="P17" s="18">
-        <v>0.321123845838051</v>
+        <v>0.1122019286359213</v>
       </c>
       <c r="Q17" s="15" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="R17" s="15" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="S17" s="16">
-        <v>0.08343490561786401</v>
+        <v>0.04761930708640676</v>
       </c>
       <c r="T17" s="17" t="s">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="U17" s="17" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="V17" s="18">
-        <v>0.1046572699656809</v>
+        <v>0.143879877592941</v>
       </c>
     </row>
     <row r="18" spans="1:22">
       <c r="A18" s="1"/>
       <c r="B18" s="9" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="D18" s="10">
-        <v>0.01667262575701411</v>
+        <v>0.04987473179653627</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="G18" s="12">
-        <v>0.05126435356716915</v>
+        <v>0.05086219797544596</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="J18" s="14">
-        <v>0.05469517205195652</v>
+        <v>0.02430062776765411</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="L18" s="15" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="M18" s="16">
-        <v>0.0419525713201313</v>
+        <v>0.01474797947225804</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="O18" s="17" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="P18" s="18">
-        <v>0.02550469312802136</v>
+        <v>0.09521830142401694</v>
       </c>
       <c r="Q18" s="15" t="s">
-        <v>157</v>
+        <v>84</v>
       </c>
       <c r="R18" s="15" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="S18" s="16">
-        <v>0.02700934048744291</v>
+        <v>0.01118399616363844</v>
       </c>
       <c r="T18" s="17" t="s">
-        <v>163</v>
+        <v>78</v>
       </c>
       <c r="U18" s="17" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="V18" s="18">
-        <v>0.08315752626727438</v>
+        <v>0.09640978042102497</v>
       </c>
     </row>
     <row r="19" spans="1:22">
       <c r="A19" s="1"/>
       <c r="B19" s="9" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="D19" s="10">
-        <v>0.009842497409378963</v>
+        <v>0.0317437720705648</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>125</v>
+        <v>62</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="G19" s="12">
-        <v>0.03407550008917475</v>
+        <v>0.03265372058267284</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="J19" s="14">
-        <v>0.02375930393691175</v>
+        <v>0.006603949294202323</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="L19" s="15" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="M19" s="16">
-        <v>0.03241575137915966</v>
+        <v>0.01377290644929883</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="O19" s="17" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="P19" s="18">
-        <v>0.00625038484321156</v>
+        <v>0.00946311695083998</v>
       </c>
       <c r="Q19" s="15" t="s">
-        <v>106</v>
+        <v>162</v>
       </c>
       <c r="R19" s="15" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="S19" s="16">
-        <v>0.02540776162414944</v>
+        <v>0.0068992184126341</v>
       </c>
       <c r="T19" s="17" t="s">
         <v>125</v>
       </c>
       <c r="U19" s="17" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="V19" s="18">
-        <v>0.01039358212145215</v>
+        <v>0.0844622033508276</v>
       </c>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="1"/>
       <c r="B20" s="9" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="D20" s="10">
-        <v>0.007878244401124671</v>
+        <v>0.01614459749654908</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="G20" s="12">
-        <v>0.01275777697881515</v>
+        <v>0.002474044923720188</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>82</v>
+        <v>110</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J20" s="14">
-        <v>0.02064651054714886</v>
+        <v>0.004602251123265434</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="L20" s="15" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="M20" s="16">
-        <v>0.02044352094467317</v>
+        <v>0.01237327038092613</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>152</v>
+        <v>130</v>
       </c>
       <c r="O20" s="17" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="P20" s="18">
-        <v>0.004396434098104411</v>
+        <v>0.002798369096688528</v>
       </c>
       <c r="Q20" s="15" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="R20" s="15" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="S20" s="16">
-        <v>0.01905840077851938</v>
+        <v>0.006219770564235963</v>
       </c>
       <c r="T20" s="17" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="U20" s="17" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="V20" s="18">
-        <v>0.009768080691354063</v>
+        <v>0.02824777427043428</v>
       </c>
     </row>
     <row r="23" spans="1:22">
       <c r="B23" s="19" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
     </row>
     <row r="24" spans="1:22">
       <c r="B24" s="20" t="s">
-        <v>54</v>
+        <v>91</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
     </row>
     <row r="25" spans="1:22">
       <c r="B25" s="20" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
     <row r="26" spans="1:22">
       <c r="B26" s="20" t="s">
-        <v>175</v>
+        <v>93</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
     </row>
     <row r="27" spans="1:22">
       <c r="B27" s="20" t="s">
-        <v>106</v>
+        <v>54</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
     </row>
     <row r="28" spans="1:22">
       <c r="B28" s="20" t="s">
-        <v>146</v>
+        <v>84</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
     </row>
     <row r="30" spans="1:22">
       <c r="B30" s="19" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D30" s="19" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
     </row>
     <row r="31" spans="1:22">
       <c r="B31" s="20" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C31" s="21" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="D31" s="22">
-        <v>0.2300628520879037</v>
+        <v>0.3151667698387779</v>
       </c>
     </row>
     <row r="32" spans="1:22">
       <c r="B32" s="20" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C32" s="21" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="D32" s="22">
-        <v>0.1453776338997468</v>
+        <v>0.3092387115404132</v>
       </c>
     </row>
     <row r="33" spans="2:4">
       <c r="B33" s="20" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C33" s="21" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D33" s="22">
-        <v>0.1313998538484508</v>
+        <v>0.2323872759461231</v>
       </c>
     </row>
     <row r="34" spans="2:4">
       <c r="B34" s="20" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C34" s="21" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="D34" s="22">
-        <v>0.1254657925945156</v>
+        <v>0.1490384494219761</v>
       </c>
     </row>
     <row r="35" spans="2:4">
       <c r="B35" s="20" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C35" s="21" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="D35" s="22">
-        <v>0.0889880309101527</v>
+        <v>0.08831714793078588</v>
       </c>
     </row>
     <row r="36" spans="2:4">
       <c r="B36" s="20" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="C36" s="21" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="D36" s="22">
-        <v>0.08364158266684991</v>
+        <v>0.03162509280719791</v>
       </c>
     </row>
     <row r="37" spans="2:4">
       <c r="B37" s="20" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="C37" s="21" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="D37" s="22">
-        <v>0.07211664960069356</v>
+        <v>0.02857736741036228</v>
       </c>
     </row>
     <row r="38" spans="2:4">
       <c r="B38" s="20" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C38" s="21" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="D38" s="22">
-        <v>0.02974995266770654</v>
+        <v>0.01743122489242259</v>
       </c>
     </row>
     <row r="39" spans="2:4">
       <c r="B39" s="20" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="C39" s="21" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="D39" s="22">
-        <v>0.01930604224885294</v>
+        <v>0.01490415797208965</v>
       </c>
     </row>
     <row r="40" spans="2:4">
       <c r="B40" s="20" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C40" s="21" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="D40" s="22">
-        <v>0.01413985476053546</v>
+        <v>0.01299230626490225</v>
       </c>
     </row>
     <row r="41" spans="2:4">
       <c r="B41" s="20" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C41" s="21" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="D41" s="22">
-        <v>0.004609674913624373</v>
+        <v>0.008797836874252044</v>
       </c>
     </row>
     <row r="42" spans="2:4">
       <c r="B42" s="20" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C42" s="21" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="D42" s="22">
-        <v>0.003299210083862153</v>
+        <v>0.007929091011501889</v>
       </c>
     </row>
     <row r="43" spans="2:4">
       <c r="B43" s="20" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C43" s="21" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="D43" s="22">
-        <v>0.002026969449046062</v>
+        <v>0.0007737487583711119</v>
       </c>
     </row>
     <row r="44" spans="2:4">
       <c r="B44" s="20" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C44" s="21" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D44" s="22">
-        <v>0.000463501528494229</v>
+        <v>0.0001679374293504444</v>
       </c>
     </row>
     <row r="45" spans="2:4">
       <c r="B45" s="20" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C45" s="21" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D45" s="22">
-        <v>2.063063667417439E-05</v>
+        <v>1.371024356058002E-05</v>
       </c>
     </row>
     <row r="46" spans="2:4">
       <c r="B46" s="20" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C46" s="20" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="D46" s="20" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
     </row>
   </sheetData>
@@ -2987,331 +2999,331 @@
     <row r="9" spans="1:22">
       <c r="A9" s="1"/>
       <c r="B9" s="9" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="D9" s="10">
-        <v>0.8027910775171649</v>
+        <v>0.2513676952331405</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="G9" s="12">
-        <v>0.1626389155993241</v>
+        <v>0.4351432667328781</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="J9" s="14">
-        <v>0.1604426458204456</v>
+        <v>0.4038855114487994</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="M9" s="16">
-        <v>0.1562392365639012</v>
+        <v>0.7688165823164254</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="O9" s="17" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="P9" s="18">
-        <v>0.1172671446167488</v>
+        <v>0.4233473171324881</v>
       </c>
       <c r="Q9" s="15" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="R9" s="15" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="S9" s="16">
-        <v>0.05508300564307848</v>
+        <v>0.1788407663498864</v>
       </c>
       <c r="T9" s="17" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="U9" s="17" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="V9" s="18">
-        <v>0.4857756780491559</v>
+        <v>0.1213569266415609</v>
       </c>
     </row>
     <row r="10" spans="1:22">
       <c r="A10" s="1"/>
       <c r="B10" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="D10" s="10">
-        <v>0.03150279257496462</v>
+        <v>0.04681208532429853</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="G10" s="12">
-        <v>0.06513238184579097</v>
+        <v>0.1107600142271736</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="J10" s="14">
-        <v>0.08149974287699031</v>
+        <v>0.1594107525162184</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="M10" s="16">
-        <v>0.09576285076653149</v>
+        <v>0.04826997477663996</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="O10" s="17" t="s">
-        <v>94</v>
+        <v>235</v>
       </c>
       <c r="P10" s="18">
-        <v>0.02282265598386415</v>
+        <v>0.08806426320310341</v>
       </c>
       <c r="Q10" s="15" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="R10" s="15" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="S10" s="16">
-        <v>0.04953337502290937</v>
+        <v>0.1302731103886665</v>
       </c>
       <c r="T10" s="17" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="U10" s="17" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="V10" s="18">
-        <v>0.02269413781204551</v>
+        <v>0.05515364839985864</v>
       </c>
     </row>
     <row r="11" spans="1:22">
       <c r="A11" s="1"/>
       <c r="B11" s="9" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>61</v>
+        <v>217</v>
       </c>
       <c r="D11" s="10">
-        <v>0.02336846430100383</v>
+        <v>0.04313024017272035</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>179</v>
+        <v>198</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>218</v>
+        <v>73</v>
       </c>
       <c r="G11" s="12">
-        <v>0.06428745211027773</v>
+        <v>0.01633140037078681</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="J11" s="14">
-        <v>0.05758110856994158</v>
+        <v>0.003943155802010206</v>
       </c>
       <c r="K11" s="15" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="L11" s="15" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="M11" s="16">
-        <v>0.08710489673387037</v>
+        <v>0.007024826624505884</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>185</v>
+        <v>202</v>
       </c>
       <c r="O11" s="17" t="s">
-        <v>232</v>
+        <v>97</v>
       </c>
       <c r="P11" s="18">
-        <v>0.01446468889150898</v>
+        <v>0.05954529915065872</v>
       </c>
       <c r="Q11" s="15" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="R11" s="15" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="S11" s="16">
-        <v>0.03386682909660605</v>
+        <v>0.04427688214158166</v>
       </c>
       <c r="T11" s="17" t="s">
-        <v>179</v>
+        <v>196</v>
       </c>
       <c r="U11" s="17" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="V11" s="18">
-        <v>0.02197775356532867</v>
+        <v>0.04852871931740719</v>
       </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1"/>
       <c r="B12" s="9" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="D12" s="10">
-        <v>0.01226281528809087</v>
+        <v>0.0347366594052005</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="G12" s="12">
-        <v>0.01589949307884133</v>
+        <v>0.002692943610744579</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="J12" s="14">
-        <v>0.0244073092107087</v>
+        <v>0.001866277195132186</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="L12" s="15" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="M12" s="16">
-        <v>0.08334979597123821</v>
+        <v>0.003583000410025348</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="O12" s="17" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="P12" s="18">
-        <v>0.01409234749548836</v>
+        <v>0.0324983654144852</v>
       </c>
       <c r="Q12" s="15" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="R12" s="15" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="S12" s="16">
-        <v>0.02432813192640289</v>
+        <v>0.02896878464171702</v>
       </c>
       <c r="T12" s="17" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="U12" s="17" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="V12" s="18">
-        <v>0.01973287907029687</v>
+        <v>0.03229008661092739</v>
       </c>
     </row>
     <row r="13" spans="1:22">
       <c r="A13" s="1"/>
       <c r="B13" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="D13" s="10">
-        <v>0.006993449591159225</v>
+        <v>0.02281597471600415</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="G13" s="12">
-        <v>0.01356724179425081</v>
+        <v>0.0007004164399890162</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="J13" s="14">
-        <v>0.01196688096354211</v>
+        <v>0.001858361991922599</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="L13" s="15" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="M13" s="16">
-        <v>0.04845439172578529</v>
+        <v>0.001564061565748191</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O13" s="17" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="P13" s="18">
-        <v>0.007183180213193961</v>
+        <v>0.02689508765127883</v>
       </c>
       <c r="Q13" s="15" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="R13" s="15" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="S13" s="16">
-        <v>0.02143687217362236</v>
+        <v>0.01268743880760511</v>
       </c>
       <c r="T13" s="17" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="U13" s="17" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="V13" s="18">
-        <v>0.01802489028220521</v>
+        <v>0.009722787711269474</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -3322,7 +3334,7 @@
         <v>51</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>53</v>
@@ -3331,7 +3343,7 @@
         <v>51</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>53</v>
@@ -3340,7 +3352,7 @@
         <v>51</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>53</v>
@@ -3349,7 +3361,7 @@
         <v>51</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="M15" s="5" t="s">
         <v>53</v>
@@ -3358,7 +3370,7 @@
         <v>51</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="P15" s="6" t="s">
         <v>53</v>
@@ -3367,7 +3379,7 @@
         <v>51</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="S15" s="5" t="s">
         <v>53</v>
@@ -3376,7 +3388,7 @@
         <v>51</v>
       </c>
       <c r="U15" s="6" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="V15" s="6" t="s">
         <v>53</v>
@@ -3385,331 +3397,331 @@
     <row r="16" spans="1:22">
       <c r="A16" s="1"/>
       <c r="B16" s="9" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="D16" s="10">
-        <v>0.05825742052771971</v>
+        <v>0.4511179547386115</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="G16" s="12">
-        <v>0.5450390573538056</v>
+        <v>0.3401852257463304</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="J16" s="14">
-        <v>0.3597144726196991</v>
+        <v>0.351433300319225</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L16" s="15" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="M16" s="16">
-        <v>0.1574917111886219</v>
+        <v>0.1123832772423979</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="O16" s="17" t="s">
-        <v>145</v>
+        <v>268</v>
       </c>
       <c r="P16" s="18">
-        <v>0.4249483974149166</v>
+        <v>0.1210301993502687</v>
       </c>
       <c r="Q16" s="15" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="R16" s="15" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="S16" s="16">
-        <v>0.5239054772124152</v>
+        <v>0.4984487229125833</v>
       </c>
       <c r="T16" s="17" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="U16" s="17" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="V16" s="18">
-        <v>0.1403891485972722</v>
+        <v>0.2425855214054666</v>
       </c>
     </row>
     <row r="17" spans="1:22">
       <c r="A17" s="1"/>
       <c r="B17" s="9" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="D17" s="10">
-        <v>0.0203785044290211</v>
+        <v>0.05514513651422041</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="G17" s="12">
-        <v>0.04194739536562973</v>
+        <v>0.0511387113638638</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="J17" s="14">
-        <v>0.08751108171934577</v>
+        <v>0.03478029649778144</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="L17" s="15" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="M17" s="16">
-        <v>0.09508754673116002</v>
+        <v>0.03254522050602798</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="O17" s="17" t="s">
-        <v>147</v>
+        <v>269</v>
       </c>
       <c r="P17" s="18">
-        <v>0.321123845838051</v>
+        <v>0.1132205664034903</v>
       </c>
       <c r="Q17" s="15" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="R17" s="15" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="S17" s="16">
-        <v>0.1100466178430627</v>
+        <v>0.05477875573740296</v>
       </c>
       <c r="T17" s="17" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="U17" s="17" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="V17" s="18">
-        <v>0.1378691720276817</v>
+        <v>0.2173383901765604</v>
       </c>
     </row>
     <row r="18" spans="1:22">
       <c r="A18" s="1"/>
       <c r="B18" s="9" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="D18" s="10">
-        <v>0.01699082930180016</v>
+        <v>0.04403327296925326</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="G18" s="12">
-        <v>0.02664292329759781</v>
+        <v>0.03769669824905665</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="J18" s="14">
-        <v>0.08435258253924061</v>
+        <v>0.02463128756659803</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="L18" s="15" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="M18" s="16">
-        <v>0.0839825389451196</v>
+        <v>0.01392394754588261</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="O18" s="17" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="P18" s="18">
-        <v>0.04448415583025574</v>
+        <v>0.1087783961624569</v>
       </c>
       <c r="Q18" s="15" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="R18" s="15" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="S18" s="16">
-        <v>0.06007573655333466</v>
+        <v>0.01801798852500427</v>
       </c>
       <c r="T18" s="17" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="U18" s="17" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="V18" s="18">
-        <v>0.09407970084417255</v>
+        <v>0.1440596209033219</v>
       </c>
     </row>
     <row r="19" spans="1:22">
       <c r="A19" s="1"/>
       <c r="B19" s="9" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D19" s="10">
-        <v>0.008080144678221249</v>
+        <v>0.01913256865663694</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G19" s="12">
-        <v>0.0118963269361282</v>
+        <v>0.001860081376886821</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="J19" s="14">
-        <v>0.03039455762788099</v>
+        <v>0.007737741691807871</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="L19" s="15" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="M19" s="16">
-        <v>0.05714326026680185</v>
+        <v>0.00528939264220349</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O19" s="17" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="P19" s="18">
-        <v>0.0172883660908145</v>
+        <v>0.008903082897459875</v>
       </c>
       <c r="Q19" s="15" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="R19" s="15" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="S19" s="16">
-        <v>0.04513386651052199</v>
+        <v>0.008390041373798559</v>
       </c>
       <c r="T19" s="17" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="U19" s="17" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="V19" s="18">
-        <v>0.01896846400474664</v>
+        <v>0.03165655834358012</v>
       </c>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="1"/>
       <c r="B20" s="9" t="s">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="D20" s="10">
-        <v>0.003767902064585219</v>
+        <v>0.006361037537777055</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="G20" s="12">
-        <v>0.01042003556451657</v>
+        <v>0.001644332597724456</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="J20" s="14">
-        <v>0.02098725306949783</v>
+        <v>0.004311592431964209</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="L20" s="15" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="M20" s="16">
-        <v>0.03811903900347461</v>
+        <v>0.002473200354035112</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="O20" s="17" t="s">
-        <v>267</v>
+        <v>157</v>
       </c>
       <c r="P20" s="18">
-        <v>0.003709464223453933</v>
+        <v>0.002798369096688528</v>
       </c>
       <c r="Q20" s="15" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="R20" s="15" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="S20" s="16">
-        <v>0.03340444452348008</v>
+        <v>0.007639637037786134</v>
       </c>
       <c r="T20" s="17" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="U20" s="17" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="V20" s="18">
-        <v>0.01327250641928099</v>
+        <v>0.02871498572850566</v>
       </c>
     </row>
   </sheetData>
